--- a/Docs/export/current/10_trang_bi.xlsx
+++ b/Docs/export/current/10_trang_bi.xlsx
@@ -24,12 +24,12 @@
     <sheet name="Trang_bi_hang" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trang_bi'!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Trang_bi'!$A$1:$Q$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Trang_bi_mo_dun'!$A$1:$J$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trang_bi_dac_tinh'!$A$1:$H$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trang_bi_dong_phu'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trang_bi_bo'!$A$1:$P$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trang_bi_thap'!$A$1:$K$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trang_bi_thap'!$A$1:$K$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Trang_bi_dac_tinh_thap'!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Trang_bi_tran'!$A$1:$E$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Trang_bi_chi_so'!$A$1:$F$28</definedName>
@@ -37,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Trang_bi_ghep'!$A$1:$G$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Trang_bi_thung'!$A$1:$R$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Trang_bi_thung_nguon'!$A$1:$H$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Trang_bi_ten'!$A$1:$G$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Trang_bi_ten'!$A$1:$G$160</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Trang_bi_hang'!$A$1:$K$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,8 +457,8 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:269 (Bases[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:271 (Bases[7])</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[16])</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.4;0.55;0.7;0.85;1</t>
+          <t>0.25;0.35;0.45;0.55;0.65</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[18])</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{"id":"armoured_tub","slot":"Armor","implicitStat":"ArmourAll","top":[0.4,0.55,0.7,0.85,1]}</t>
+          <t>{"id":"armoured_tub","slot":"Armor","implicitStat":"ArmourAll","top":[0.25,0.35,0.45,0.55,0.65]}</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:274 (Bases[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:276 (Bases[10])</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:330 (Bases[37])</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:272 (Bases[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:274 (Bases[8])</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:319 (Bases[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[36])</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[14])</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:313 (Bases[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:321 (Bases[31])</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:310 (Bases[26])</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -983,169 +983,166 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>extended_ammo_rack</t>
+          <t>energy_dissipation_liner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Giá đạn mở rộng</t>
+          <t>Tấm lót tản năng lượng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Magazine</t>
+          <t>ResistEnergy</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.1;0.15;0.2;0.25;0.3</t>
+          <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:273 (Bases[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[20])</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>{"id":"extended_ammo_rack","slot":"Loader","implicitStat":"Magazine","top":[0.1,0.15,0.2,0.25,0.3]}</t>
+          <t>{"id":"energy_dissipation_liner","slot":"Armor","implicitStat":"ResistEnergy","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fire_extinguisher</t>
+          <t>extended_ammo_rack</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bình chữa cháy</t>
+          <t>Giá đạn mở rộng</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>StatusDuration</t>
+          <t>Magazine</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.1;0.18;0.26;0.34;0.42</t>
+          <t>0.1;0.15;0.2;0.25;0.3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:275 (Bases[9])</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>{"id":"fire_extinguisher","slot":"Repair","implicitStat":"StatusDuration","top":[0.1,0.18,0.26,0.34,0.42]}</t>
+          <t>{"id":"extended_ammo_rack","slot":"Loader","implicitStat":"Magazine","top":[0.1,0.15,0.2,0.25,0.3]}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fire_retardant_hull</t>
+          <t>field_service_interface</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thân xe chống cháy</t>
+          <t>Bộ tiếp nhận sửa chữa dã chiến</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ResistFire</t>
+          <t>RepairReceived</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Repair</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.08;0.12;0.16;0.2;0.25</t>
+          <t>0.02;0.03;0.04;0.06;0.08</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:324 (Bases[33])</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>{"id":"fire_retardant_hull","slot":"Armor","implicitStat":"ResistFire","top":[0.08,0.12,0.16,0.2,0.25]}</t>
+          <t>{"id":"field_service_interface","slot":"Repair","implicitStat":"RepairReceived","top":[0.02,0.03,0.04,0.06,0.08]}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>flanking_rounds</t>
+          <t>fire_extinguisher</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Đạn đánh hông</t>
+          <t>Bình chữa cháy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DamageFlank</t>
+          <t>StatusDuration</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Repair</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.05;0.08;0.12;0.16;0.2</t>
+          <t>0.1;0.18;0.26;0.34;0.42</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:268 (Bases[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[32])</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>{"id":"flanking_rounds","slot":"Weapon","implicitStat":"DamageFlank","top":[0.05,0.08,0.12,0.16,0.2]}</t>
+          <t>{"id":"fire_extinguisher","slot":"Repair","implicitStat":"StatusDuration","top":[0.1,0.18,0.26,0.34,0.42]}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>frontal_wedge</t>
+          <t>fire_retardant_hull</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Giáp nêm mặt trước</t>
+          <t>Thân xe chống cháy</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ResistFrontal</t>
-        </is>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
+          <t>ResistFire</t>
+        </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1154,158 +1151,148 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.05;0.08;0.11;0.15;0.18</t>
+          <t>0.08;0.12;0.16;0.2;0.25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:295 (Bases[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[17])</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>{"id":"frontal_wedge","slot":"Armor","implicitStat":"ResistFrontal","top":[0.05,0.08,0.11,0.15,0.18],"Plating":true}</t>
+          <t>{"id":"fire_retardant_hull","slot":"Armor","implicitStat":"ResistFire","top":[0.08,0.12,0.16,0.2,0.25]}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gun_stabiliser</t>
+          <t>flanking_rounds</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bộ ổn định pháo</t>
+          <t>Đạn đánh hông</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SpreadMoving</t>
+          <t>DamageFlank</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Optics</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.1;0.15;0.2;0.25;0.3</t>
+          <t>0.05;0.08;0.12;0.16;0.2</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:318 (Bases[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:270 (Bases[6])</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>{"id":"gun_stabiliser","slot":"Optics","implicitStat":"SpreadMoving","top":[0.1,0.15,0.2,0.25,0.3]}</t>
+          <t>{"id":"flanking_rounds","slot":"Weapon","implicitStat":"DamageFlank","top":[0.05,0.08,0.12,0.16,0.2]}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hair_trigger</t>
+          <t>frontal_wedge</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cò nhạy</t>
+          <t>Giáp nêm mặt trước</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FireRate</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0;0;-0.1;-0.12;-0.14</t>
-        </is>
+          <t>ResistFrontal</t>
+        </is>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0;0;0.1;0.12;0.15</t>
+          <t>0.05;0.08;0.11;0.15;0.18</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:276 (Bases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[22])</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>{"id":"hair_trigger","slot":"Loader","implicitStat":"FireRate","top":[0,0,0.1,0.12,0.15],"Penalty":"Spread","PenaltyTop":[0,0,-0.1,-0.12,-0.14],"MinRarity":2}</t>
+          <t>{"id":"frontal_wedge","slot":"Armor","implicitStat":"ResistFrontal","top":[0.05,0.08,0.11,0.15,0.18],"Plating":true}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>he_frag_filler</t>
+          <t>gun_stabiliser</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thuốc nổ phá mảnh</t>
+          <t>Bộ ổn định pháo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>SpreadMoving</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Optics</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.05;0.08;0.12;0.16;0.2</t>
+          <t>0.1;0.15;0.2;0.25;0.3</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:261 (Bases[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:328 (Bases[35])</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>{"id":"he_frag_filler","slot":"Weapon","implicitStat":"Splash","top":[0.05,0.08,0.12,0.16,0.2]}</t>
+          <t>{"id":"gun_stabiliser","slot":"Optics","implicitStat":"SpreadMoving","top":[0.1,0.15,0.2,0.25,0.3]}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>heavy_barrel</t>
+          <t>hair_trigger</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nòng nặng</t>
+          <t>Cò nhạy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>FireRate</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1313,17 +1300,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Speed</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0;0;-0.05;-0.06;-0.07</t>
+          <t>0;0;-0.08;-0.1;-0.12</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1333,250 +1320,247 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:264 (Bases[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[12])</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>{"id":"heavy_barrel","slot":"Weapon","implicitStat":"Range","top":[0,0,0.08,0.1,0.12],"Penalty":"Speed","PenaltyTop":[0,0,-0.05,-0.06,-0.07],"MinRarity":2}</t>
+          <t>{"id":"hair_trigger","slot":"Loader","implicitStat":"FireRate","top":[0,0,0.08,0.1,0.12],"Penalty":"Spread","PenaltyTop":[0,0,-0.08,-0.1,-0.12],"MinRarity":2}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>laser_rangefinder</t>
+          <t>he_frag_filler</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Máy đo xa la-de</t>
+          <t>Thuốc nổ phá mảnh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SpreadLong</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Optics</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.08;0.12;0.16;0.2;0.25</t>
+          <t>0.05;0.08;0.12;0.16;0.2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:261 (Bases[2])</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>{"id":"laser_rangefinder","slot":"Optics","implicitStat":"SpreadLong","top":[0.08,0.12,0.16,0.2,0.25]}</t>
+          <t>{"id":"he_frag_filler","slot":"Weapon","implicitStat":"Splash","top":[0.05,0.08,0.12,0.16,0.2]}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>laser_warning</t>
+          <t>heavy_barrel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cảnh báo la-de</t>
-        </is>
-      </c>
-      <c r="C23" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
+          <t>Nòng nặng</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LaserWarning</t>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0;0;-0.03;-0.04;-0.05</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Optics</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6;6.5;7;7.5;8</t>
+          <t>0;0;0.07;0.09;0.1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:326 (Bases[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:266 (Bases[5])</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>{"id":"laser_warning","slot":"Optics","implicitStat":"LaserWarning","top":[6,6.5,7,7.5,8],"Flat":true,"Hidden":true}</t>
+          <t>{"id":"heavy_barrel","slot":"Weapon","implicitStat":"Range","top":[0,0,0.07,0.09,0.1],"Penalty":"Speed","PenaltyTop":[0,0,-0.03,-0.04,-0.05],"MinRarity":2}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>long_barrel</t>
+          <t>laser_rangefinder</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nòng dài</t>
+          <t>Máy đo xa la-de</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>SpreadLong</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Optics</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.02;0.03;0.04;0.06;0.08</t>
+          <t>0.08;0.12;0.16;0.2;0.25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:258 (Bases[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[34])</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>{"id":"long_barrel","slot":"Weapon","implicitStat":"Range","top":[0.02,0.03,0.04,0.06,0.08]}</t>
+          <t>{"id":"laser_rangefinder","slot":"Optics","implicitStat":"SpreadLong","top":[0.08,0.12,0.16,0.2,0.25]}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>monolith_plate</t>
+          <t>laser_warning</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tấm giáp nguyên khối</t>
-        </is>
+          <t>Cảnh báo la-de</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0;0;-0.04;-0.05;-0.06</t>
+          <t>LaserWarning</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Optics</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0;0;0;0;0</t>
+          <t>6;6.5;7;7.5;8</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Bases[39])</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{"id":"monolith_plate","slot":"Armor","implicitStat":"Count","top":[0,0,0,0,0],"Penalty":"Speed","PenaltyTop":[0,0,-0.04,-0.05,-0.06],"MinRarity":2,"MainScale":1.8,"NoSubs":true}</t>
+          <t>{"id":"laser_warning","slot":"Optics","implicitStat":"LaserWarning","top":[6,6.5,7,7.5,8],"Flat":true,"Hidden":true}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>overhead_screen</t>
+          <t>long_barrel</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mái che chống pháo</t>
+          <t>Nòng dài</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ResistIndirect</t>
-        </is>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
+          <t>Range</t>
+        </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.06;0.09;0.13;0.17;0.22</t>
+          <t>0.02;0.03;0.04;0.06;0.08</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:258 (Bases[0])</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>{"id":"overhead_screen","slot":"Armor","implicitStat":"ResistIndirect","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
+          <t>{"id":"long_barrel","slot":"Weapon","implicitStat":"Range","top":[0.02,0.03,0.04,0.06,0.08]}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>overtuned_engine</t>
+          <t>monolith_plate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Động cơ độ quá mức</t>
+          <t>Tấm giáp nguyên khối</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Speed</t>
-        </is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1.8</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
       </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1586,490 +1570,580 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0;0;0.1;0.12;0.15</t>
+          <t>0;0;0;0;0</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:293 (Bases[19])</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{"id":"overtuned_engine","slot":"Engine","implicitStat":"Speed","top":[0,0,0.1,0.12,0.15],"Penalty":"Health","PenaltyTop":[0,0,-0.04,-0.05,-0.06],"MinRarity":2}</t>
+          <t>{"id":"monolith_plate","slot":"Armor","implicitStat":"Count","top":[0,0,0,0,0],"Penalty":"Speed","PenaltyTop":[0,0,-0.04,-0.05,-0.06],"MinRarity":2,"MainScale":1.8,"NoSubs":true}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>proximity_fuze</t>
+          <t>overhead_screen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ngòi nổ cận đích</t>
+          <t>Mái che chống pháo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DamageVsAir</t>
-        </is>
+          <t>ResistIndirect</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>1</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.05;0.08;0.12;0.16;0.2</t>
+          <t>0.06;0.09;0.13;0.17;0.22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:262 (Bases[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:304 (Bases[24])</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>{"id":"proximity_fuze","slot":"Weapon","implicitStat":"DamageVsAir","top":[0.05,0.08,0.12,0.16,0.2]}</t>
+          <t>{"id":"overhead_screen","slot":"Armor","implicitStat":"ResistIndirect","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>radar_absorbent_coating</t>
+          <t>overtuned_engine</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lớp phủ chống radar</t>
+          <t>Động cơ độ quá mức</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>LockRange</t>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0;0;-0.03;-0.04;-0.05</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0.06;0.09;0.13;0.16;0.2</t>
+          <t>0;0;0.08;0.1;0.12</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[28])</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{"id":"radar_absorbent_coating","slot":"Armor","implicitStat":"LockRange","top":[0.06,0.09,0.13,0.16,0.2]}</t>
+          <t>{"id":"overtuned_engine","slot":"Engine","implicitStat":"Speed","top":[0,0,0.08,0.1,0.12],"Penalty":"Health","PenaltyTop":[0,0,-0.03,-0.04,-0.05],"MinRarity":2}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>reverse_gearbox</t>
+          <t>proximity_fuze</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hộp số lùi</t>
+          <t>Ngòi nổ cận đích</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ReverseSpeed</t>
+          <t>DamageVsAir</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.15;0.2;0.28;0.34;0.4</t>
+          <t>0.05;0.08;0.12;0.16;0.2</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:309 (Bases[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:262 (Bases[3])</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>{"id":"reverse_gearbox","slot":"Engine","implicitStat":"ReverseSpeed","top":[0.15,0.2,0.28,0.34,0.4]}</t>
+          <t>{"id":"proximity_fuze","slot":"Weapon","implicitStat":"DamageVsAir","top":[0.05,0.08,0.12,0.16,0.2]}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>salvo_rack</t>
+          <t>radar_absorbent_coating</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Giá phóng loạt</t>
+          <t>Lớp phủ chống radar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SalvoInterval</t>
+          <t>LockRange</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.1;0.15;0.2;0.25;0.3</t>
+          <t>0.06;0.09;0.13;0.16;0.2</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:275 (Bases[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[21])</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>{"id":"salvo_rack","slot":"Loader","implicitStat":"SalvoInterval","top":[0.1,0.15,0.2,0.25,0.3]}</t>
+          <t>{"id":"radar_absorbent_coating","slot":"Armor","implicitStat":"LockRange","top":[0.06,0.09,0.13,0.16,0.2]}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>signal_relay</t>
+          <t>reverse_gearbox</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trạm chuyển tiếp tín hiệu</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Vision</t>
+          <t>Hộp số lùi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CaptureRate</t>
+          <t>ReverseSpeed</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Optics</t>
+          <t>Engine</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.1;0.15;0.2;0.25;0.3</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0.03;0.04;0.06;0.08;0.1</t>
+          <t>0.15;0.2;0.28;0.34;0.4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[29])</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>{"id":"signal_relay","slot":"Optics","implicitStat":"CaptureRate","top":[0.1,0.15,0.2,0.25,0.3],"Implicit2":"Vision","Top2":[0.03,0.04,0.06,0.08,0.1]}</t>
+          <t>{"id":"reverse_gearbox","slot":"Engine","implicitStat":"ReverseSpeed","top":[0.15,0.2,0.28,0.34,0.4]}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>slat_cage</t>
+          <t>salvo_rack</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lồng chống rốc-két</t>
+          <t>Giá phóng loạt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ResistRocket</t>
-        </is>
-      </c>
-      <c r="L33" t="b">
-        <v>1</v>
+          <t>SalvoInterval</t>
+        </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.06;0.09;0.13;0.17;0.22</t>
+          <t>0.1;0.15;0.2;0.25;0.3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:296 (Bases[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:277 (Bases[11])</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>{"id":"slat_cage","slot":"Armor","implicitStat":"ResistRocket","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
+          <t>{"id":"salvo_rack","slot":"Loader","implicitStat":"SalvoInterval","top":[0.1,0.15,0.2,0.25,0.3]}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>spall_liner</t>
+          <t>signal_relay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lớp lót chống mảnh</t>
+          <t>Trạm chuyển tiếp tín hiệu</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Vision</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ResistHighExplosive</t>
+          <t>CaptureRate</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Optics</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.04;0.06;0.09;0.12;0.15</t>
+          <t>0.1;0.15;0.2;0.25;0.3</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0.03;0.04;0.06;0.08;0.1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:283 (Bases[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[38])</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>{"id":"spall_liner","slot":"Armor","implicitStat":"ResistHighExplosive","top":[0.04,0.06,0.09,0.12,0.15]}</t>
+          <t>{"id":"signal_relay","slot":"Optics","implicitStat":"CaptureRate","top":[0.1,0.15,0.2,0.25,0.3],"Implicit2":"Vision","Top2":[0.03,0.04,0.06,0.08,0.1]}</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>spare_magazine</t>
+          <t>slat_cage</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Băng đạn dự phòng</t>
-        </is>
-      </c>
-      <c r="C35" t="b">
+          <t>Lồng chống rốc-két</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ResistRocket</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
         <v>1</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>SpareMagazine</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.4;0.55;0.7;0.85;1</t>
+          <t>0.06;0.09;0.13;0.17;0.22</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[23])</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>{"id":"spare_magazine","slot":"Loader","implicitStat":"SpareMagazine","top":[0.4,0.55,0.7,0.85,1],"Flat":true}</t>
+          <t>{"id":"slat_cage","slot":"Armor","implicitStat":"ResistRocket","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>toolbox</t>
+          <t>spall_liner</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hộp dụng cụ</t>
+          <t>Lớp lót chống mảnh</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RegenDelay</t>
+          <t>ResistHighExplosive</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1;1.5;2;2.5;3</t>
+          <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[15])</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>{"id":"toolbox","slot":"Repair","implicitStat":"RegenDelay","top":[1,1.5,2,2.5,3]}</t>
+          <t>{"id":"spall_liner","slot":"Armor","implicitStat":"ResistHighExplosive","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>transit_gearbox</t>
+          <t>spare_magazine</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Hộp số hành quân</t>
-        </is>
+          <t>Băng đạn dự phòng</t>
+        </is>
+      </c>
+      <c r="C37" t="b">
+        <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>TransitSpeed</t>
+          <t>SpareMagazine</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Engine</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.05;0.08;0.12;0.16;0.2</t>
+          <t>0.4;0.55;0.7;0.85;1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:305 (Bases[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[13])</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>{"id":"transit_gearbox","slot":"Engine","implicitStat":"TransitSpeed","top":[0.05,0.08,0.12,0.16,0.2]}</t>
+          <t>{"id":"spare_magazine","slot":"Loader","implicitStat":"SpareMagazine","top":[0.4,0.55,0.7,0.85,1],"Flat":true}</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tungsten_penetrator</t>
+          <t>toolbox</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lõi xuyên vonfram</t>
+          <t>Hộp dụng cụ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Penetration</t>
+          <t>RegenDelay</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Repair</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.4;0.55;0.7;0.85;1</t>
+          <t>1;1.5;2;2.5;3</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:260 (Bases[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[30])</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{"id":"tungsten_penetrator","slot":"Weapon","implicitStat":"Penetration","top":[0.4,0.55,0.7,0.85,1]}</t>
+          <t>{"id":"toolbox","slot":"Repair","implicitStat":"RegenDelay","top":[1,1.5,2,2.5,3]}</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>transit_gearbox</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hộp số hành quân</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>TransitSpeed</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Engine</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0.05;0.08;0.12;0.16;0.2</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[27])</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{"id":"transit_gearbox","slot":"Engine","implicitStat":"TransitSpeed","top":[0.05,0.08,0.12,0.16,0.2]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>tungsten_penetrator</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lõi xuyên vonfram</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Penetration</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0.4;0.55;0.7;0.85;1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:260 (Bases[1])</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{"id":"tungsten_penetrator","slot":"Weapon","implicitStat":"Penetration","top":[0.4,0.55,0.7,0.85,1]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>underbelly_armor</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Giáp gầm</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>ResistBlast</t>
         </is>
       </c>
-      <c r="L39" t="b">
+      <c r="L41" t="b">
         <v>1</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Armor</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>0.05;0.08;0.11;0.15;0.18</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[24])</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[25])</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
         <is>
           <t>{"id":"underbelly_armor","slot":"Armor","implicitStat":"ResistBlast","top":[0.05,0.08,0.11,0.15,0.18],"Plating":true}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q39"/>
+  <autoFilter ref="A1:Q41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5499,7 +5573,7 @@
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
@@ -5571,7 +5645,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:447 (Brands[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:458 (Brands[4])</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -5604,7 +5678,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[12])</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -5637,7 +5711,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:452 (Brands[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[9])</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -5670,7 +5744,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:449 (Brands[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[6])</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -5703,7 +5777,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Brands[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[0])</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -5736,7 +5810,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Brands[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[1])</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -5769,7 +5843,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:446 (Brands[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[3])</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -5802,7 +5876,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[10])</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -5835,7 +5909,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:450 (Brands[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[7])</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -5868,7 +5942,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:451 (Brands[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[8])</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -5901,7 +5975,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:448 (Brands[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[5])</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -5934,7 +6008,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Brands[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:456 (Brands[2])</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -5967,7 +6041,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[11])</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -6000,7 +6074,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:269 (Bases[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:271 (Bases[7])</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -6033,7 +6107,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[16])</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -6066,7 +6140,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[18])</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -6099,7 +6173,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:274 (Bases[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:276 (Bases[10])</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -6165,7 +6239,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:330 (Bases[37])</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -6198,7 +6272,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:272 (Bases[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:274 (Bases[8])</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -6231,7 +6305,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:319 (Bases[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[36])</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -6264,7 +6338,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[14])</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -6297,7 +6371,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:313 (Bases[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:321 (Bases[31])</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -6330,7 +6404,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:310 (Bases[26])</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -6338,7 +6412,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>co_ban/extended_ammo_rack</t>
+          <t>co_ban/energy_dissipation_liner</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6348,22 +6422,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>gear.base.extended_ammo_rack</t>
+          <t>gear.base.energy_dissipation_liner</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Extended Ammo Rack</t>
+          <t>Energy Dissipation Liner</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Giá đạn mở rộng</t>
+          <t>Tấm lót tản năng lượng</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:273 (Bases[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[20])</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -6371,7 +6445,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>co_ban/fire_extinguisher</t>
+          <t>co_ban/extended_ammo_rack</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6381,22 +6455,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>gear.base.fire_extinguisher</t>
+          <t>gear.base.extended_ammo_rack</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Halon System</t>
+          <t>Extended Ammo Rack</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bình chữa cháy</t>
+          <t>Giá đạn mở rộng</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:275 (Bases[9])</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -6404,7 +6478,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>co_ban/fire_retardant_hull</t>
+          <t>co_ban/field_service_interface</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6414,22 +6488,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>gear.base.fire_retardant_hull</t>
+          <t>gear.base.field_service_interface</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fire-Retardant Hull</t>
+          <t>Field Service Interface</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thân xe chống cháy</t>
+          <t>Bộ tiếp nhận sửa chữa dã chiến</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:324 (Bases[33])</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -6437,7 +6511,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>co_ban/flanking_rounds</t>
+          <t>co_ban/fire_extinguisher</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6447,22 +6521,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gear.base.flanking_rounds</t>
+          <t>gear.base.fire_extinguisher</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Flanking Rounds</t>
+          <t>Halon System</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Đạn đánh hông</t>
+          <t>Bình chữa cháy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:268 (Bases[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[32])</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -6470,7 +6544,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>co_ban/frontal_wedge</t>
+          <t>co_ban/fire_retardant_hull</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6480,22 +6554,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>gear.base.frontal_wedge</t>
+          <t>gear.base.fire_retardant_hull</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Frontal Wedge</t>
+          <t>Fire-Retardant Hull</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Giáp nêm mặt trước</t>
+          <t>Thân xe chống cháy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:295 (Bases[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[17])</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -6503,7 +6577,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>co_ban/gun_stabiliser</t>
+          <t>co_ban/flanking_rounds</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6513,22 +6587,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gear.base.gun_stabiliser</t>
+          <t>gear.base.flanking_rounds</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gun Stabiliser</t>
+          <t>Flanking Rounds</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bộ ổn định pháo</t>
+          <t>Đạn đánh hông</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:318 (Bases[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:270 (Bases[6])</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -6536,7 +6610,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>co_ban/hair_trigger</t>
+          <t>co_ban/frontal_wedge</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6546,22 +6620,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>gear.base.hair_trigger</t>
+          <t>gear.base.frontal_wedge</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hair Trigger</t>
+          <t>Frontal Wedge</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cò nhạy</t>
+          <t>Giáp nêm mặt trước</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:276 (Bases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[22])</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -6569,7 +6643,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>co_ban/he_frag_filler</t>
+          <t>co_ban/gun_stabiliser</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6579,22 +6653,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>gear.base.he_frag_filler</t>
+          <t>gear.base.gun_stabiliser</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>HE-Frag Filler</t>
+          <t>Gun Stabiliser</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thuốc nổ phá mảnh</t>
+          <t>Bộ ổn định pháo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:261 (Bases[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:328 (Bases[35])</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -6602,7 +6676,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>co_ban/heavy_barrel</t>
+          <t>co_ban/hair_trigger</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6612,22 +6686,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>gear.base.heavy_barrel</t>
+          <t>gear.base.hair_trigger</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Heavy Barrel</t>
+          <t>Hair Trigger</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nòng nặng</t>
+          <t>Cò nhạy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:264 (Bases[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[12])</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -6635,7 +6709,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>co_ban/laser_rangefinder</t>
+          <t>co_ban/he_frag_filler</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6645,22 +6719,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gear.base.laser_rangefinder</t>
+          <t>gear.base.he_frag_filler</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Laser Rangefinder</t>
+          <t>HE-Frag Filler</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Máy đo xa la-de</t>
+          <t>Thuốc nổ phá mảnh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:261 (Bases[2])</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -6668,7 +6742,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>co_ban/laser_warning</t>
+          <t>co_ban/heavy_barrel</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6678,22 +6752,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>gear.base.laser_warning</t>
+          <t>gear.base.heavy_barrel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Laser Warning Receiver</t>
+          <t>Heavy Barrel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cảnh báo la-de</t>
+          <t>Nòng nặng</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:326 (Bases[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:266 (Bases[5])</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -6701,7 +6775,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>co_ban/long_barrel</t>
+          <t>co_ban/laser_rangefinder</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6711,22 +6785,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>gear.base.long_barrel</t>
+          <t>gear.base.laser_rangefinder</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Long Barrel</t>
+          <t>Laser Rangefinder</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nòng dài</t>
+          <t>Máy đo xa la-de</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:258 (Bases[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[34])</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -6734,7 +6808,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>co_ban/monolith_plate</t>
+          <t>co_ban/laser_warning</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6744,22 +6818,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>gear.base.monolith_plate</t>
+          <t>gear.base.laser_warning</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Monolith Plate</t>
+          <t>Laser Warning Receiver</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tấm giáp nguyên khối</t>
+          <t>Cảnh báo la-de</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Bases[39])</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -6767,7 +6841,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>co_ban/overhead_screen</t>
+          <t>co_ban/long_barrel</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6777,22 +6851,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>gear.base.overhead_screen</t>
+          <t>gear.base.long_barrel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Overhead Screen</t>
+          <t>Long Barrel</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mái che chống pháo</t>
+          <t>Nòng dài</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:258 (Bases[0])</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -6800,7 +6874,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>co_ban/overtuned_engine</t>
+          <t>co_ban/monolith_plate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6810,22 +6884,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>gear.base.overtuned_engine</t>
+          <t>gear.base.monolith_plate</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Overtuned Engine</t>
+          <t>Monolith Plate</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Động cơ độ quá mức</t>
+          <t>Tấm giáp nguyên khối</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:293 (Bases[19])</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -6833,7 +6907,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>co_ban/proximity_fuze</t>
+          <t>co_ban/overhead_screen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6843,22 +6917,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>gear.base.proximity_fuze</t>
+          <t>gear.base.overhead_screen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Proximity Fuze</t>
+          <t>Overhead Screen</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ngòi nổ cận đích</t>
+          <t>Mái che chống pháo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:262 (Bases[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:304 (Bases[24])</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -6866,7 +6940,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>co_ban/radar_absorbent_coating</t>
+          <t>co_ban/overtuned_engine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6876,22 +6950,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>gear.base.radar_absorbent_coating</t>
+          <t>gear.base.overtuned_engine</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Radar-Absorbent Coating</t>
+          <t>Overtuned Engine</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lớp phủ chống radar</t>
+          <t>Động cơ độ quá mức</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[28])</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -6899,7 +6973,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>co_ban/reverse_gearbox</t>
+          <t>co_ban/proximity_fuze</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6909,22 +6983,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>gear.base.reverse_gearbox</t>
+          <t>gear.base.proximity_fuze</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Reverse Gearbox</t>
+          <t>Proximity Fuze</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hộp số lùi</t>
+          <t>Ngòi nổ cận đích</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:309 (Bases[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:262 (Bases[3])</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -6932,7 +7006,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>co_ban/salvo_rack</t>
+          <t>co_ban/radar_absorbent_coating</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6942,22 +7016,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>gear.base.salvo_rack</t>
+          <t>gear.base.radar_absorbent_coating</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Salvo Rack</t>
+          <t>Radar-Absorbent Coating</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Giá phóng loạt</t>
+          <t>Lớp phủ chống radar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:275 (Bases[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[21])</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -6965,7 +7039,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>co_ban/signal_relay</t>
+          <t>co_ban/reverse_gearbox</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6975,22 +7049,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>gear.base.signal_relay</t>
+          <t>gear.base.reverse_gearbox</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Signal Relay</t>
+          <t>Reverse Gearbox</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trạm chuyển tiếp tín hiệu</t>
+          <t>Hộp số lùi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[29])</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -6998,7 +7072,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>co_ban/slat_cage</t>
+          <t>co_ban/salvo_rack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7008,22 +7082,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>gear.base.slat_cage</t>
+          <t>gear.base.salvo_rack</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Slat Cage</t>
+          <t>Salvo Rack</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lồng chống rốc-két</t>
+          <t>Giá phóng loạt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:296 (Bases[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:277 (Bases[11])</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -7031,7 +7105,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>co_ban/spall_liner</t>
+          <t>co_ban/signal_relay</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7041,22 +7115,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gear.base.spall_liner</t>
+          <t>gear.base.signal_relay</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Spall Liner</t>
+          <t>Signal Relay</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lớp lót chống mảnh</t>
+          <t>Trạm chuyển tiếp tín hiệu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:283 (Bases[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[38])</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7064,7 +7138,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>co_ban/spare_magazine</t>
+          <t>co_ban/slat_cage</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7074,22 +7148,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gear.base.spare_magazine</t>
+          <t>gear.base.slat_cage</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Spare Magazine</t>
+          <t>Slat Cage</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Băng đạn dự phòng</t>
+          <t>Lồng chống rốc-két</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[23])</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -7097,7 +7171,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>co_ban/toolbox</t>
+          <t>co_ban/spall_liner</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7107,22 +7181,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>gear.base.toolbox</t>
+          <t>gear.base.spall_liner</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Toolbox</t>
+          <t>Spall Liner</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hộp dụng cụ</t>
+          <t>Lớp lót chống mảnh</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[15])</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -7130,7 +7204,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>co_ban/transit_gearbox</t>
+          <t>co_ban/spare_magazine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7140,22 +7214,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>gear.base.transit_gearbox</t>
+          <t>gear.base.spare_magazine</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Transit Gearbox</t>
+          <t>Spare Magazine</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hộp số hành quân</t>
+          <t>Băng đạn dự phòng</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:305 (Bases[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[13])</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -7163,7 +7237,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>co_ban/tungsten_penetrator</t>
+          <t>co_ban/toolbox</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7173,22 +7247,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gear.base.tungsten_penetrator</t>
+          <t>gear.base.toolbox</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tungsten Core</t>
+          <t>Toolbox</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lõi xuyên vonfram</t>
+          <t>Hộp dụng cụ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:260 (Bases[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[30])</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -7196,7 +7270,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>co_ban/underbelly_armor</t>
+          <t>co_ban/transit_gearbox</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7206,22 +7280,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gear.base.underbelly_armor</t>
+          <t>gear.base.transit_gearbox</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Underbelly Armour</t>
+          <t>Transit Gearbox</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Giáp gầm</t>
+          <t>Hộp số hành quân</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[27])</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -7229,32 +7303,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>co_ban_thap/airburst_shells</t>
+          <t>co_ban/tungsten_penetrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>co_ban_thap</t>
+          <t>co_ban</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gear.base.airburst_shells</t>
+          <t>gear.base.tungsten_penetrator</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Fragmentation Shells</t>
+          <t>Tungsten Core</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Đạn nổ phân mảnh</t>
+          <t>Lõi xuyên vonfram</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:25 (TowerBases[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:260 (Bases[1])</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -7262,32 +7336,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>co_ban_thap/ammo_handling</t>
+          <t>co_ban/underbelly_armor</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>co_ban_thap</t>
+          <t>co_ban</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gear.base.ammo_handling</t>
+          <t>gear.base.underbelly_armor</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ammunition Handling</t>
+          <t>Underbelly Armour</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hệ thống nạp đạn</t>
+          <t>Giáp gầm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:39 (TowerBases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[25])</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -7295,7 +7369,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>co_ban_thap/ammo_hoist</t>
+          <t>co_ban_thap/airburst_shells</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7305,22 +7379,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gear.base.ammo_hoist</t>
+          <t>gear.base.airburst_shells</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ammunition Hoist</t>
+          <t>Fragmentation Shells</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tời tiếp đạn</t>
+          <t>Đạn nổ phân mảnh</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:26 (TowerBases[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:25 (TowerBases[3])</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -7328,7 +7402,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>co_ban_thap/blast_walls</t>
+          <t>co_ban_thap/ammo_handling</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7338,22 +7412,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>gear.base.blast_walls</t>
+          <t>gear.base.ammo_handling</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Blast Walls</t>
+          <t>Ammunition Handling</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tường chắn nổ</t>
+          <t>Hệ thống nạp đạn</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:31 (TowerBases[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:43 (TowerBases[13])</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -7361,7 +7435,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>co_ban_thap/composite_casemate</t>
+          <t>co_ban_thap/ammo_hoist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7371,22 +7445,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gear.base.composite_casemate</t>
+          <t>gear.base.ammo_hoist</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Composite Casemate</t>
+          <t>Ammunition Hoist</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lô cốt tổng hợp</t>
+          <t>Tời tiếp đạn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:30 (TowerBases[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:27 (TowerBases[4])</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -7394,7 +7468,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>co_ban_thap/engineer_bay</t>
+          <t>co_ban_thap/blast_walls</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7404,22 +7478,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gear.base.engineer_bay</t>
+          <t>gear.base.blast_walls</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Engineer Bay</t>
+          <t>Blast Walls</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Trạm công binh</t>
+          <t>Tường chắn nổ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:33 (TowerBases[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:32 (TowerBases[7])</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -7427,7 +7501,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>co_ban_thap/flak_proximity_fuze</t>
+          <t>co_ban_thap/composite_casemate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7437,22 +7511,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gear.base.flak_proximity_fuze</t>
+          <t>gear.base.composite_casemate</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Flak Proximity Fuze</t>
+          <t>Composite Casemate</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ngòi cận đích phòng không</t>
+          <t>Lô cốt tổng hợp</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:24 (TowerBases[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:31 (TowerBases[6])</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -7460,7 +7534,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>co_ban_thap/fortress_barrel</t>
+          <t>co_ban_thap/engineer_bay</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7470,22 +7544,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>gear.base.fortress_barrel</t>
+          <t>gear.base.engineer_bay</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Fortress Barrel</t>
+          <t>Engineer Bay</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nòng pháo công sự</t>
+          <t>Trạm công binh</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:21 (TowerBases[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:34 (TowerBases[9])</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -7493,7 +7567,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>co_ban_thap/reinforced_concrete</t>
+          <t>co_ban_thap/flak_proximity_fuze</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7503,22 +7577,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>gear.base.reinforced_concrete</t>
+          <t>gear.base.flak_proximity_fuze</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Reinforced Concrete</t>
+          <t>Flak Proximity Fuze</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bê tông cốt thép</t>
+          <t>Ngòi cận đích phòng không</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:29 (TowerBases[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:24 (TowerBases[2])</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -7526,7 +7600,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>co_ban_thap/sabot_rounds</t>
+          <t>co_ban_thap/fortress_barrel</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7536,22 +7610,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>gear.base.sabot_rounds</t>
+          <t>gear.base.fortress_barrel</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sabot Rounds</t>
+          <t>Fortress Barrel</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Đạn xuyên dưới cỡ</t>
+          <t>Nòng pháo công sự</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:23 (TowerBases[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:21 (TowerBases[0])</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -7559,7 +7633,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>co_ban_thap/search_radar</t>
+          <t>co_ban_thap/grounding_mesh</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7569,17 +7643,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>gear.base.search_radar</t>
+          <t>gear.base.grounding_mesh</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Search Radar</t>
+          <t>Grounding Mesh</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Radar tìm kiếm</t>
+          <t>Lưới tiếp địa năng lượng</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7592,7 +7666,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>co_ban_thap/slat_screens</t>
+          <t>co_ban_thap/reinforced_concrete</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7602,22 +7676,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>gear.base.slat_screens</t>
+          <t>gear.base.reinforced_concrete</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Slat Screens</t>
+          <t>Reinforced Concrete</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lưới chắn rốc-két</t>
+          <t>Bê tông cốt thép</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:32 (TowerBases[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:30 (TowerBases[5])</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -7625,7 +7699,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>co_ban_thap/traverse_motors</t>
+          <t>co_ban_thap/sabot_rounds</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7635,22 +7709,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>gear.base.traverse_motors</t>
+          <t>gear.base.sabot_rounds</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Traverse Motors</t>
+          <t>Sabot Rounds</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mô-tơ xoay tháp</t>
+          <t>Đạn xuyên dưới cỡ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:37 (TowerBases[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:23 (TowerBases[1])</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7658,32 +7732,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dac_tinh/AblativeLayer</t>
+          <t>co_ban_thap/search_radar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>dac_tinh</t>
+          <t>co_ban_thap</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>trait.AblativeLayer</t>
+          <t>gear.base.search_radar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ablative Layer</t>
+          <t>Search Radar</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lớp giáp hy sinh</t>
+          <t>Radar tìm kiếm</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:39 (TowerBases[11])</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7691,32 +7765,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>dac_tinh/AdaptivePlating</t>
+          <t>co_ban_thap/slat_screens</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dac_tinh</t>
+          <t>co_ban_thap</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>trait.AdaptivePlating</t>
+          <t>gear.base.slat_screens</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Adaptive Plating</t>
+          <t>Slat Screens</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Giáp thích ứng</t>
+          <t>Lưới chắn rốc-két</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:33 (TowerBases[8])</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7724,32 +7798,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dac_tinh/AegisBarrier</t>
+          <t>co_ban_thap/traverse_motors</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>dac_tinh</t>
+          <t>co_ban_thap</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>trait.AegisBarrier</t>
+          <t>gear.base.traverse_motors</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Aegis Barrier</t>
+          <t>Traverse Motors</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Khiên Aegis</t>
+          <t>Mô-tơ xoay tháp</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:40 (TowerBases[12])</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7757,7 +7831,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dac_tinh/AfterburnerReserve</t>
+          <t>dac_tinh/AblativeLayer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7767,22 +7841,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>trait.AfterburnerReserve</t>
+          <t>trait.AblativeLayer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Afterburner Reserve</t>
+          <t>Ablative Layer</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Đốt sau dự phòng</t>
+          <t>Lớp giáp hy sinh</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[24])</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -7790,7 +7864,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>dac_tinh/AmmoCarrier</t>
+          <t>dac_tinh/AdaptivePlating</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7800,22 +7874,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>trait.AmmoCarrier</t>
+          <t>trait.AdaptivePlating</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ammo Carrier</t>
+          <t>Adaptive Plating</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Xe chở đạn</t>
+          <t>Giáp thích ứng</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[22])</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7823,7 +7897,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dac_tinh/AngledGlacis</t>
+          <t>dac_tinh/AegisBarrier</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7833,22 +7907,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>trait.AngledGlacis</t>
+          <t>trait.AegisBarrier</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Angled Glacis</t>
+          <t>Aegis Barrier</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Giáp nghiêng</t>
+          <t>Khiên Aegis</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[18])</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7856,7 +7930,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dac_tinh/ClusterWarhead</t>
+          <t>dac_tinh/AfterburnerReserve</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7866,22 +7940,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>trait.ClusterWarhead</t>
+          <t>trait.AfterburnerReserve</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cluster Warhead</t>
+          <t>Afterburner Reserve</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Đầu đạn chùm</t>
+          <t>Đốt sau dự phòng</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Traits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[31])</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7889,7 +7963,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dac_tinh/CombatWelder</t>
+          <t>dac_tinh/AmmoCarrier</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7899,22 +7973,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>trait.CombatWelder</t>
+          <t>trait.AmmoCarrier</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Combat Welder</t>
+          <t>Ammo Carrier</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Thợ hàn chiến trường</t>
+          <t>Xe chở đạn</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:397 (Traits[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:409 (Traits[37])</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7922,7 +7996,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dac_tinh/CounterBatteryRadar</t>
+          <t>dac_tinh/AngledGlacis</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7932,22 +8006,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>trait.CounterBatteryRadar</t>
+          <t>trait.AngledGlacis</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Counter-Battery Radar</t>
+          <t>Angled Glacis</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Radar phản pháo</t>
+          <t>Giáp nghiêng</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[42])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[25])</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7955,7 +8029,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dac_tinh/DamageControl</t>
+          <t>dac_tinh/ClusterWarhead</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7965,22 +8039,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>trait.DamageControl</t>
+          <t>trait.ClusterWarhead</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Damage Control</t>
+          <t>Cluster Warhead</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kiểm soát hư hại</t>
+          <t>Đầu đạn chùm</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[3])</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7988,7 +8062,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dac_tinh/DarkCrown</t>
+          <t>dac_tinh/CombatWelder</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7998,22 +8072,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>trait.DarkCrown</t>
+          <t>trait.CombatWelder</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Dark Crown</t>
+          <t>Combat Welder</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vương miện bóng tối</t>
+          <t>Thợ hàn chiến trường</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[35])</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8021,7 +8095,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dac_tinh/EmergencyRepairKit</t>
+          <t>dac_tinh/CounterBatteryRadar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8031,22 +8105,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>trait.EmergencyRepairKit</t>
+          <t>trait.CounterBatteryRadar</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Emergency Repair Kit</t>
+          <t>Counter-Battery Radar</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bộ sửa khẩn cấp</t>
+          <t>Radar phản pháo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[42])</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8054,7 +8128,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dac_tinh/EwJammer</t>
+          <t>dac_tinh/DamageControl</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8064,22 +8138,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>trait.EwJammer</t>
+          <t>trait.DamageControl</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EW Jammer</t>
+          <t>Damage Control</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gây nhiễu điện tử</t>
+          <t>Kiểm soát hư hại</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[43])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[38])</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -8087,7 +8161,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dac_tinh/Executioner</t>
+          <t>dac_tinh/DarkCrown</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8097,22 +8171,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>trait.Executioner</t>
+          <t>trait.DarkCrown</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Executioner</t>
+          <t>Dark Crown</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Đao phủ</t>
+          <t>Vương miện bóng tối</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:365 (Traits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[21])</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8120,7 +8194,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>dac_tinh/FieldMechanics</t>
+          <t>dac_tinh/EmergencyRepairKit</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8130,22 +8204,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>trait.FieldMechanics</t>
+          <t>trait.EmergencyRepairKit</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Field Mechanics</t>
+          <t>Emergency Repair Kit</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Thợ máy dã chiến</t>
+          <t>Bộ sửa khẩn cấp</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[34])</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8153,7 +8227,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dac_tinh/FireControlComputer</t>
+          <t>dac_tinh/EwJammer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8163,22 +8237,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>trait.FireControlComputer</t>
+          <t>trait.EwJammer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Fire-Control Computer</t>
+          <t>EW Jammer</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Máy tính điều khiển hỏa lực</t>
+          <t>Gây nhiễu điện tử</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[44])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Traits[43])</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -8186,7 +8260,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>dac_tinh/GhillieMode</t>
+          <t>dac_tinh/Executioner</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8196,22 +8270,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>trait.GhillieMode</t>
+          <t>trait.Executioner</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ghillie Mode</t>
+          <t>Executioner</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chế độ ngụy trang</t>
+          <t>Đao phủ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:404 (Traits[41])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[7])</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8219,7 +8293,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>dac_tinh/GuardianLink</t>
+          <t>dac_tinh/FieldMechanics</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8229,22 +8303,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>trait.GuardianLink</t>
+          <t>trait.FieldMechanics</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Guardian Link</t>
+          <t>Field Mechanics</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Liên kết hộ vệ</t>
+          <t>Thợ máy dã chiến</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[33])</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8252,7 +8326,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>dac_tinh/HotSwap</t>
+          <t>dac_tinh/FireControlComputer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8262,22 +8336,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>trait.HotSwap</t>
+          <t>trait.FireControlComputer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Hot Swap</t>
+          <t>Fire-Control Computer</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Thay băng nóng</t>
+          <t>Máy tính điều khiển hỏa lực</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[44])</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8285,7 +8359,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>dac_tinh/HullDownCrew</t>
+          <t>dac_tinh/GhillieMode</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8295,22 +8369,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>trait.HullDownCrew</t>
+          <t>trait.GhillieMode</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Hull-Down Crew</t>
+          <t>Ghillie Mode</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Kíp ẩn thân</t>
+          <t>Chế độ ngụy trang</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[41])</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8318,7 +8392,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>dac_tinh/IncendiaryRounds</t>
+          <t>dac_tinh/GuardianLink</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8328,22 +8402,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>trait.IncendiaryRounds</t>
+          <t>trait.GuardianLink</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Incendiary Rounds</t>
+          <t>Guardian Link</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Đạn cháy</t>
+          <t>Liên kết hộ vệ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Traits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[20])</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8351,7 +8425,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>dac_tinh/KillReload</t>
+          <t>dac_tinh/HotSwap</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8361,22 +8435,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>trait.KillReload</t>
+          <t>trait.HotSwap</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kill Reload</t>
+          <t>Hot Swap</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hạ là nạp</t>
+          <t>Thay băng nóng</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[15])</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8384,7 +8458,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dac_tinh/LaserDesignator</t>
+          <t>dac_tinh/HullDownCrew</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8394,22 +8468,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>trait.LaserDesignator</t>
+          <t>trait.HullDownCrew</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Laser Designator</t>
+          <t>Hull-Down Crew</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chỉ thị la-de</t>
+          <t>Kíp ẩn thân</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[40])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[11])</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8417,7 +8491,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>dac_tinh/MomentumGun</t>
+          <t>dac_tinh/IncendiaryRounds</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8427,22 +8501,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>trait.MomentumGun</t>
+          <t>trait.IncendiaryRounds</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Momentum Gun</t>
+          <t>Incendiary Rounds</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pháo tích đà</t>
+          <t>Đạn cháy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:364 (Traits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:369 (Traits[1])</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8450,7 +8524,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>dac_tinh/NitroDash</t>
+          <t>dac_tinh/KillReload</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8460,22 +8534,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>trait.NitroDash</t>
+          <t>trait.KillReload</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Nitro Dash</t>
+          <t>Kill Reload</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bứt tốc</t>
+          <t>Hạ là nạp</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[12])</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8483,7 +8557,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dac_tinh/OpeningSalvo</t>
+          <t>dac_tinh/LaserDesignator</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8493,22 +8567,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>trait.OpeningSalvo</t>
+          <t>trait.LaserDesignator</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Opening Salvo</t>
+          <t>Laser Designator</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Loạt mở màn</t>
+          <t>Chỉ thị la-de</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:363 (Traits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[40])</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8516,7 +8590,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>dac_tinh/OverpressureChamber</t>
+          <t>dac_tinh/MomentumGun</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8526,22 +8600,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>trait.OverpressureChamber</t>
+          <t>trait.MomentumGun</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Overpressure Chamber</t>
+          <t>Momentum Gun</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Buồng quá áp</t>
+          <t>Pháo tích đà</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[6])</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8549,7 +8623,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>dac_tinh/RapidDeployment</t>
+          <t>dac_tinh/NitroDash</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8559,22 +8633,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>trait.RapidDeployment</t>
+          <t>trait.NitroDash</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Rapid Deployment</t>
+          <t>Nitro Dash</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Triển khai nhanh</t>
+          <t>Bứt tốc</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[27])</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -8582,7 +8656,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>dac_tinh/RapidResponse</t>
+          <t>dac_tinh/OpeningSalvo</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8592,22 +8666,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>trait.RapidResponse</t>
+          <t>trait.OpeningSalvo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Rapid Response</t>
+          <t>Opening Salvo</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Phản ứng nhanh</t>
+          <t>Loạt mở màn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[5])</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -8615,7 +8689,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>dac_tinh/ReactiveBlocks</t>
+          <t>dac_tinh/OverpressureChamber</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8625,22 +8699,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>trait.ReactiveBlocks</t>
+          <t>trait.OverpressureChamber</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Reactive Blocks</t>
+          <t>Overpressure Chamber</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Khối giáp phản ứng</t>
+          <t>Buồng quá áp</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[14])</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -8648,7 +8722,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>dac_tinh/Rearguard</t>
+          <t>dac_tinh/RapidDeployment</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8658,22 +8732,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>trait.Rearguard</t>
+          <t>trait.RapidDeployment</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Rearguard</t>
+          <t>Rapid Deployment</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chặn hậu</t>
+          <t>Triển khai nhanh</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[29])</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -8681,7 +8755,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dac_tinh/RicochetShells</t>
+          <t>dac_tinh/RapidResponse</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8691,22 +8765,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>trait.RicochetShells</t>
+          <t>trait.RapidResponse</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ricochet Shells</t>
+          <t>Rapid Response</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Đạn nảy</t>
+          <t>Phản ứng nhanh</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Traits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[13])</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -8714,7 +8788,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>dac_tinh/SalvageTeam</t>
+          <t>dac_tinh/ReactiveBlocks</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8724,22 +8798,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>trait.SalvageTeam</t>
+          <t>trait.ReactiveBlocks</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Salvage Team</t>
+          <t>Reactive Blocks</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Đội thu hồi</t>
+          <t>Khối giáp phản ứng</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[23])</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -8747,7 +8821,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dac_tinh/ShootAndScoot</t>
+          <t>dac_tinh/Rearguard</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8757,22 +8831,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>trait.ShootAndScoot</t>
+          <t>trait.Rearguard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Shoot-and-Scoot</t>
+          <t>Rearguard</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bắn rồi chạy</t>
+          <t>Chặn hậu</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[32])</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -8780,7 +8854,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dac_tinh/ShredderRounds</t>
+          <t>dac_tinh/RicochetShells</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8790,22 +8864,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>trait.ShredderRounds</t>
+          <t>trait.RicochetShells</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Shredder Rounds</t>
+          <t>Ricochet Shells</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Đạn xé giáp</t>
+          <t>Đạn nảy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Traits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[2])</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -8813,7 +8887,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dac_tinh/SiegeAnchor</t>
+          <t>dac_tinh/SalvageTeam</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8823,22 +8897,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>trait.SiegeAnchor</t>
+          <t>trait.SalvageTeam</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Siege Anchor</t>
+          <t>Salvage Team</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Neo công thành</t>
+          <t>Đội thu hồi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[36])</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -8846,7 +8920,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dac_tinh/SkywardPintle</t>
+          <t>dac_tinh/ShootAndScoot</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8856,22 +8930,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>trait.SkywardPintle</t>
+          <t>trait.ShootAndScoot</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Skyward Pintle</t>
+          <t>Shoot-and-Scoot</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Giá súng phòng không</t>
+          <t>Bắn rồi chạy</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[28])</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -8879,7 +8953,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dac_tinh/SuppressionRounds</t>
+          <t>dac_tinh/ShredderRounds</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8889,22 +8963,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>trait.SuppressionRounds</t>
+          <t>trait.ShredderRounds</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Suppression Rounds</t>
+          <t>Shredder Rounds</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Đạn áp chế</t>
+          <t>Đạn xé giáp</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:367 (Traits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[4])</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -8912,7 +8986,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dac_tinh/SuppressiveFire</t>
+          <t>dac_tinh/SiegeAnchor</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8922,22 +8996,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>trait.SuppressiveFire</t>
+          <t>trait.SiegeAnchor</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Suppressive Fire</t>
+          <t>Siege Anchor</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hỏa lực chế áp</t>
+          <t>Neo công thành</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[26])</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -8945,7 +9019,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dac_tinh/TandemWarhead</t>
+          <t>dac_tinh/SkywardPintle</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8955,22 +9029,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>trait.TandemWarhead</t>
+          <t>trait.SkywardPintle</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tandem Warhead</t>
+          <t>Skyward Pintle</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Đầu nổ kép</t>
+          <t>Giá súng phòng không</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:366 (Traits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[16])</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -8978,7 +9052,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dac_tinh/ThermalImager</t>
+          <t>dac_tinh/SuppressionRounds</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8988,22 +9062,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>trait.ThermalImager</t>
+          <t>trait.SuppressionRounds</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Thermal Imager</t>
+          <t>Suppression Rounds</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kính ảnh nhiệt</t>
+          <t>Đạn áp chế</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[9])</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -9011,7 +9085,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dac_tinh/TwinFeed</t>
+          <t>dac_tinh/SuppressiveFire</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9021,22 +9095,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>trait.TwinFeed</t>
+          <t>trait.SuppressiveFire</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Twin Feed</t>
+          <t>Suppressive Fire</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nạp kép</t>
+          <t>Hỏa lực chế áp</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Traits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[10])</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -9044,7 +9118,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dac_tinh/Unbreakable</t>
+          <t>dac_tinh/TandemWarhead</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9054,22 +9128,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>trait.Unbreakable</t>
+          <t>trait.TandemWarhead</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Unbreakable</t>
+          <t>Tandem Warhead</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bất khuất</t>
+          <t>Đầu nổ kép</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:379 (Traits[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[8])</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -9077,7 +9151,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dac_tinh/Vengeance</t>
+          <t>dac_tinh/ThermalImager</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9087,22 +9161,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>trait.Vengeance</t>
+          <t>trait.ThermalImager</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Vengeance</t>
+          <t>Thermal Imager</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Trả thù</t>
+          <t>Kính ảnh nhiệt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[39])</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -9110,7 +9184,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dac_tinh/VolatileFuelTanks</t>
+          <t>dac_tinh/TwinFeed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9120,22 +9194,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>trait.VolatileFuelTanks</t>
+          <t>trait.TwinFeed</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Volatile Fuel Tanks</t>
+          <t>Twin Feed</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bình xăng dễ nổ</t>
+          <t>Nạp kép</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[0])</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -9143,32 +9217,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/AblativeLayer@thap</t>
+          <t>dac_tinh/Unbreakable</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>dac_tinh_thap</t>
+          <t>dac_tinh</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>trait.AblativeLayer</t>
+          <t>trait.Unbreakable</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ablative Layer</t>
+          <t>Unbreakable</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lớp giáp hy sinh</t>
+          <t>Bất khuất</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[19])</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -9176,32 +9250,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/AegisBarrier@thap</t>
+          <t>dac_tinh/Vengeance</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>dac_tinh_thap</t>
+          <t>dac_tinh</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>trait.AegisBarrier</t>
+          <t>trait.Vengeance</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Aegis Barrier</t>
+          <t>Vengeance</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Khiên Aegis</t>
+          <t>Trả thù</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:58 (TowerTraits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[17])</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -9209,32 +9283,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/Executioner@thap</t>
+          <t>dac_tinh/VolatileFuelTanks</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dac_tinh_thap</t>
+          <t>dac_tinh</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>trait.Executioner</t>
+          <t>trait.VolatileFuelTanks</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Executioner</t>
+          <t>Volatile Fuel Tanks</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Đao phủ</t>
+          <t>Bình xăng dễ nổ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:52 (TowerTraits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[30])</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -9242,7 +9316,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/LaserDesignator@thap</t>
+          <t>dac_tinh_thap/AblativeLayer@thap</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9252,22 +9326,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>trait.LaserDesignator</t>
+          <t>trait.AblativeLayer</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Laser Designator</t>
+          <t>Ablative Layer</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chỉ thị la-de</t>
+          <t>Lớp giáp hy sinh</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[6])</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -9275,7 +9349,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/OpeningSalvo@thap</t>
+          <t>dac_tinh_thap/AegisBarrier@thap</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9285,22 +9359,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>trait.OpeningSalvo</t>
+          <t>trait.AegisBarrier</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Opening Salvo</t>
+          <t>Aegis Barrier</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Loạt mở màn</t>
+          <t>Khiên Aegis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:53 (TowerTraits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[5])</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -9308,7 +9382,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/TowerBackupGenerator@thap</t>
+          <t>dac_tinh_thap/Executioner@thap</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9318,22 +9392,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>trait.TowerBackupGenerator</t>
+          <t>trait.Executioner</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Backup Generator</t>
+          <t>Executioner</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Máy phát dự phòng</t>
+          <t>Đao phủ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[1])</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -9341,7 +9415,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/TowerCounterBattery@thap</t>
+          <t>dac_tinh_thap/LaserDesignator@thap</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9351,22 +9425,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>trait.TowerCounterBattery</t>
+          <t>trait.LaserDesignator</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Counter-Battery</t>
+          <t>Laser Designator</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Phản pháo</t>
+          <t>Chỉ thị la-de</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[9])</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -9374,7 +9448,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/TowerFireLink@thap</t>
+          <t>dac_tinh_thap/OpeningSalvo@thap</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9384,22 +9458,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>trait.TowerFireLink</t>
+          <t>trait.OpeningSalvo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Fire Link</t>
+          <t>Opening Salvo</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Liên kết hỏa lực</t>
+          <t>Loạt mở màn</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:51 (TowerTraits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[2])</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -9407,7 +9481,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/TowerModular@thap</t>
+          <t>dac_tinh_thap/TowerBackupGenerator@thap</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9417,22 +9491,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>trait.TowerModular</t>
+          <t>trait.TowerBackupGenerator</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Modular</t>
+          <t>Backup Generator</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lắp ghép</t>
+          <t>Máy phát dự phòng</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[8])</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -9440,7 +9514,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dac_tinh_thap/TowerSmokeLaunchers@thap</t>
+          <t>dac_tinh_thap/TowerCounterBattery@thap</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9450,22 +9524,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>trait.TowerSmokeLaunchers</t>
+          <t>trait.TowerCounterBattery</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Smoke Launchers</t>
+          <t>Counter-Battery</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ống phóng khói</t>
+          <t>Phản pháo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:65 (TowerTraits[7])</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -9473,32 +9547,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dong_phu/CaptureRate</t>
+          <t>dac_tinh_thap/TowerFireLink@thap</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>dong_phu</t>
+          <t>dac_tinh_thap</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>stat.line.CaptureRate</t>
+          <t>trait.TowerFireLink</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>+{percent}% capture rate</t>
+          <t>Fire Link</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>+{percent}% tốc độ chiếm cứ điểm</t>
+          <t>Liên kết hỏa lực</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[0])</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -9506,32 +9580,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dong_phu/Cooldowns</t>
+          <t>dac_tinh_thap/TowerModular@thap</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>dong_phu</t>
+          <t>dac_tinh_thap</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>stat.line.Cooldowns</t>
+          <t>trait.TowerModular</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-{percent}% skill and module cooldowns</t>
+          <t>Modular</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>-{percent}% hồi chiêu kỹ năng và mô-đun</t>
+          <t>Lắp ghép</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[3])</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -9539,32 +9613,32 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dong_phu/Damage</t>
+          <t>dac_tinh_thap/TowerSmokeLaunchers@thap</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>dong_phu</t>
+          <t>dac_tinh_thap</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>stat.line.Damage</t>
+          <t>trait.TowerSmokeLaunchers</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>+{percent}% damage</t>
+          <t>Smoke Launchers</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương</t>
+          <t>Ống phóng khói</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Subs[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[4])</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -9572,7 +9646,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dong_phu/DamageVsAir</t>
+          <t>dong_phu/CaptureRate</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9582,22 +9656,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>stat.line.DamageVsAir</t>
+          <t>stat.line.CaptureRate</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>+{percent}% damage vs aircraft</t>
+          <t>+{percent}% capture rate</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên máy bay</t>
+          <t>+{percent}% tốc độ chiếm cứ điểm</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Subs[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[20])</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -9605,7 +9679,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dong_phu/DamageVsHeavy</t>
+          <t>dong_phu/Cooldowns</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9615,22 +9689,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>stat.line.DamageVsHeavy</t>
+          <t>stat.line.Cooldowns</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>+{percent}% damage vs heavy armour (levels 3-4)</t>
+          <t>-{percent}% skill and module cooldowns</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên giáp cấp 3–4</t>
+          <t>-{percent}% hồi chiêu kỹ năng và mô-đun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Subs[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[21])</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -9638,7 +9712,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dong_phu/DamageVsLight</t>
+          <t>dong_phu/Damage</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9648,22 +9722,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>stat.line.DamageVsLight</t>
+          <t>stat.line.Damage</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>+{percent}% damage vs light armour (levels 0-2)</t>
+          <t>+{percent}% damage</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên giáp cấp 0–2</t>
+          <t>+{percent}% sát thương</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Subs[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[5])</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -9671,7 +9745,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dong_phu/DamageVsStructure</t>
+          <t>dong_phu/DamageVsAir</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9681,22 +9755,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>stat.line.DamageVsStructure</t>
+          <t>stat.line.DamageVsAir</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>+{percent}% damage vs structures</t>
+          <t>+{percent}% damage vs aircraft</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên công trình</t>
+          <t>+{percent}% sát thương lên máy bay</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Subs[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[2])</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -9704,7 +9778,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>dong_phu/FireRate</t>
+          <t>dong_phu/DamageVsHeavy</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9714,22 +9788,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>stat.line.FireRate</t>
+          <t>stat.line.DamageVsHeavy</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>+{percent}% fire rate</t>
+          <t>+{percent}% damage vs heavy vehicles (chassis armour class 3-5, whichever face is hit)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>+{percent}% tốc độ bắn</t>
+          <t>+{percent}% sát thương lên xe nặng (lớp giáp thân xe 3–5, trúng mặt nào cũng tính)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:417 (Subs[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[1])</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -9737,7 +9811,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>dong_phu/Health</t>
+          <t>dong_phu/DamageVsLight</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9747,22 +9821,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>stat.line.Health</t>
+          <t>stat.line.DamageVsLight</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>+{percent}% health</t>
+          <t>+{percent}% damage vs light vehicles (chassis armour class 0-2)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>+{percent}% máu</t>
+          <t>+{percent}% sát thương lên xe nhẹ (lớp giáp thân xe 0–2)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[0])</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -9770,7 +9844,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>dong_phu/Magazine</t>
+          <t>dong_phu/DamageVsStructure</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9780,22 +9854,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>stat.line.Magazine</t>
+          <t>stat.line.DamageVsStructure</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>+{percent}% magazine size</t>
+          <t>+{percent}% damage vs structures</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>+{percent}% sức chứa băng đạn</t>
+          <t>+{percent}% sát thương lên công trình</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[3])</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -9803,7 +9877,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>dong_phu/MagazineReload</t>
+          <t>dong_phu/FireRate</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9813,22 +9887,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>stat.line.MagazineReload</t>
+          <t>stat.line.FireRate</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>-{percent}% magazine reload time</t>
+          <t>+{percent}% fire rate</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-{percent}% thời gian nạp băng</t>
+          <t>+{percent}% tốc độ bắn</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[4])</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -9836,7 +9910,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>dong_phu/ProjectileSpeed</t>
+          <t>dong_phu/Health</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9846,22 +9920,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>stat.line.ProjectileSpeed</t>
+          <t>stat.line.Health</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>+{percent}% shell velocity</t>
+          <t>+{percent}% health</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>+{percent}% tốc độ đạn</t>
+          <t>+{percent}% máu</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:422 (Subs[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[12])</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -9869,7 +9943,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>dong_phu/Range</t>
+          <t>dong_phu/Magazine</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9879,22 +9953,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>stat.line.Range</t>
+          <t>stat.line.Magazine</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>+{percent}% range</t>
+          <t>+{percent}% magazine size</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>+{percent}% tầm bắn</t>
+          <t>+{percent}% sức chứa băng đạn</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:419 (Subs[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[10])</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -9902,7 +9976,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>dong_phu/Regen</t>
+          <t>dong_phu/MagazineReload</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9912,22 +9986,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>stat.line.Regen</t>
+          <t>stat.line.MagazineReload</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Repairs {percent}% health a second out of combat</t>
+          <t>-{percent}% magazine reload time</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hồi {percent}% máu mỗi giây khi ngoài giao tranh</t>
+          <t>-{percent}% thời gian nạp băng</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[11])</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -9935,7 +10009,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>dong_phu/ResistFire</t>
+          <t>dong_phu/ProjectileSpeed</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9945,22 +10019,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>stat.line.ResistFire</t>
+          <t>stat.line.ProjectileSpeed</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>-{percent}% fire damage, shorter burns</t>
+          <t>+{percent}% shell velocity</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-{percent}% sát thương lửa, cháy ngắn hơn</t>
+          <t>+{percent}% tốc độ đạn</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[9])</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -9968,7 +10042,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>dong_phu/ResistFragmentation</t>
+          <t>dong_phu/Range</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9978,22 +10052,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>stat.line.ResistFragmentation</t>
+          <t>stat.line.Range</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-{percent}% fragmentation damage</t>
+          <t>+{percent}% range</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>-{percent}% sát thương mảnh</t>
+          <t>+{percent}% tầm bắn</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[6])</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -10001,7 +10075,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>dong_phu/ResistHighExplosive</t>
+          <t>dong_phu/Regen</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10011,22 +10085,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>stat.line.ResistHighExplosive</t>
+          <t>stat.line.Regen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>-{percent}% high-explosive damage</t>
+          <t>Repairs {percent}% health a second out of combat</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-{percent}% sát thương nổ mạnh</t>
+          <t>Hồi {percent}% máu mỗi giây khi ngoài giao tranh</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[22])</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -10034,7 +10108,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>dong_phu/ResistKinetic</t>
+          <t>dong_phu/ResistFire</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10044,22 +10118,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>stat.line.ResistKinetic</t>
+          <t>stat.line.ResistFire</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>-{percent}% kinetic damage (bullets, cannon and tank rounds)</t>
+          <t>-{percent}% fire damage, shorter burns</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-{percent}% sát thương động năng (đạn súng, pháo, đạn xuyên)</t>
+          <t>-{percent}% sát thương lửa, cháy ngắn hơn</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[16])</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -10067,7 +10141,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>dong_phu/ResistShapedCharge</t>
+          <t>dong_phu/ResistFragmentation</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10077,22 +10151,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>stat.line.ResistShapedCharge</t>
+          <t>stat.line.ResistFragmentation</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>-{percent}% shaped-charge damage</t>
+          <t>-{percent}% fragmentation damage</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-{percent}% sát thương nổ lõm</t>
+          <t>-{percent}% sát thương mảnh</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[17])</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -10100,7 +10174,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>dong_phu/Speed</t>
+          <t>dong_phu/ResistHighExplosive</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10110,22 +10184,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>stat.line.Speed</t>
+          <t>stat.line.ResistHighExplosive</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>+{percent}% speed</t>
+          <t>-{percent}% high-explosive damage</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>+{percent}% tốc độ</t>
+          <t>-{percent}% sát thương nổ mạnh</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[15])</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -10133,7 +10207,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>dong_phu/Spread</t>
+          <t>dong_phu/ResistKinetic</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10143,22 +10217,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>stat.line.Spread</t>
+          <t>stat.line.ResistKinetic</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-{percent}% spread</t>
+          <t>-{percent}% kinetic damage (bullets, cannon and tank rounds)</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>-{percent}% độ tản mát</t>
+          <t>-{percent}% sát thương động năng (đạn súng, pháo, đạn xuyên)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:421 (Subs[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[13])</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -10166,7 +10240,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>dong_phu/TurretRate</t>
+          <t>dong_phu/ResistShapedCharge</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10176,22 +10250,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>stat.line.TurretRate</t>
+          <t>stat.line.ResistShapedCharge</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>+{percent}% turret traverse</t>
+          <t>-{percent}% shaped-charge damage</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>+{percent}% tốc độ xoay tháp pháo</t>
+          <t>-{percent}% sát thương nổ lõm</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[14])</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -10199,7 +10273,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>dong_phu/Vision</t>
+          <t>dong_phu/Speed</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10209,22 +10283,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>stat.line.Vision</t>
+          <t>stat.line.Speed</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>+{percent}% vision</t>
+          <t>+{percent}% speed</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>+{percent}% tầm nhìn</t>
+          <t>+{percent}% tốc độ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:420 (Subs[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[18])</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -10232,32 +10306,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mo_dun/AegisDome</t>
+          <t>dong_phu/Spread</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>mo_dun</t>
+          <t>dong_phu</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>special.AegisDome</t>
+          <t>stat.line.Spread</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Aegis Dome</t>
+          <t>-{percent}% spread</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Vòm Aegis</t>
+          <t>-{percent}% độ tản mát</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[8])</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -10265,32 +10339,32 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>mo_dun/AutoRepair</t>
+          <t>dong_phu/TurretRate</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mo_dun</t>
+          <t>dong_phu</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>special.AutoRepair</t>
+          <t>stat.line.TurretRate</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Auto-Repair</t>
+          <t>+{percent}% turret traverse</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tự sửa chữa</t>
+          <t>+{percent}% tốc độ xoay tháp pháo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:337 (Modules[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[19])</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -10298,32 +10372,32 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>mo_dun/DecoyLauncher</t>
+          <t>dong_phu/Vision</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>mo_dun</t>
+          <t>dong_phu</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>special.DecoyLauncher</t>
+          <t>stat.line.Vision</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Decoy Launcher</t>
+          <t>+{percent}% vision</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bệ phóng mồi nhử</t>
+          <t>+{percent}% tầm nhìn</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:351 (Modules[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[7])</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -10331,7 +10405,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>mo_dun/DroneEscort</t>
+          <t>mo_dun/AegisDome</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10341,22 +10415,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>special.DroneEscort</t>
+          <t>special.AegisDome</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Drone Escort</t>
+          <t>Aegis Dome</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Drone hộ tống</t>
+          <t>Vòm Aegis</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:345 (Modules[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[11])</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -10364,7 +10438,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>mo_dun/EmpPayload</t>
+          <t>mo_dun/AutoRepair</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10374,22 +10448,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>special.EmpPayload</t>
+          <t>special.AutoRepair</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EMP Payload</t>
+          <t>Auto-Repair</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Đầu nổ EMP</t>
+          <t>Tự sửa chữa</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[1])</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -10397,7 +10471,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>mo_dun/FlareDispenser</t>
+          <t>mo_dun/DecoyLauncher</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10407,22 +10481,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>special.FlareDispenser</t>
+          <t>special.DecoyLauncher</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Flare Dispenser</t>
+          <t>Decoy Launcher</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mồi bẫy nhiệt</t>
+          <t>Bệ phóng mồi nhử</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:344 (Modules[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[12])</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -10430,7 +10504,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>mo_dun/MineDispenser</t>
+          <t>mo_dun/DroneEscort</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10440,22 +10514,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>special.MineDispenser</t>
+          <t>special.DroneEscort</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Mine Dispenser</t>
+          <t>Drone Escort</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Máy rải mìn</t>
+          <t>Drone hộ tống</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[6])</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -10463,7 +10537,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>mo_dun/RallyHorn</t>
+          <t>mo_dun/EmpPayload</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10473,22 +10547,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>special.RallyHorn</t>
+          <t>special.EmpPayload</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Rally Horn</t>
+          <t>EMP Payload</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Kèn tập hợp</t>
+          <t>Đầu nổ EMP</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:349 (Modules[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:356 (Modules[7])</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -10496,7 +10570,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>mo_dun/ReactiveArmor</t>
+          <t>mo_dun/FlareDispenser</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10506,22 +10580,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>special.ReactiveArmor</t>
+          <t>special.FlareDispenser</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Reactive Armour</t>
+          <t>Flare Dispenser</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Giáp phản ứng nổ</t>
+          <t>Mồi bẫy nhiệt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Modules[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:354 (Modules[5])</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -10529,7 +10603,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>mo_dun/SmokeDischarger</t>
+          <t>mo_dun/MineDispenser</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10539,22 +10613,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>special.SmokeDischarger</t>
+          <t>special.MineDispenser</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Smoke Dischargers</t>
+          <t>Mine Dispenser</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ống phóng khói</t>
+          <t>Máy rải mìn</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:340 (Modules[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:357 (Modules[8])</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -10562,7 +10636,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>mo_dun/TrophyAps</t>
+          <t>mo_dun/RallyHorn</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10572,22 +10646,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>special.TrophyAps</t>
+          <t>special.RallyHorn</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Trophy APS</t>
+          <t>Rally Horn</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hệ thống Trophy APS</t>
+          <t>Kèn tập hợp</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:343 (Modules[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[10])</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -10595,7 +10669,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>mo_dun/UplinkBarrage</t>
+          <t>mo_dun/ReactiveArmor</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10605,22 +10679,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>special.UplinkBarrage</t>
+          <t>special.ReactiveArmor</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Uplink Barrage</t>
+          <t>Reactive Armour</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Pháo kích vệ tinh</t>
+          <t>Giáp phản ứng nổ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:352 (Modules[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[0])</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -10628,7 +10702,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>mo_dun/VeteranCrew</t>
+          <t>mo_dun/SmokeDischarger</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10638,22 +10712,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>special.VeteranCrew</t>
+          <t>special.SmokeDischarger</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Veteran Crew</t>
+          <t>Smoke Dischargers</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Kíp lái kỳ cựu</t>
+          <t>Ống phóng khói</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:338 (Modules[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[3])</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -10661,38 +10735,137 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>mo_dun/TrophyAps</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>mo_dun</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>special.TrophyAps</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Trophy APS</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Hệ thống Trophy APS</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[4])</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>mo_dun/UplinkBarrage</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>mo_dun</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>special.UplinkBarrage</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Uplink Barrage</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pháo kích vệ tinh</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[13])</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>mo_dun/VeteranCrew</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>mo_dun</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>special.VeteranCrew</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Veteran Crew</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Kíp lái kỳ cựu</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[2])</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>mo_dun/WarProfiteer</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>mo_dun</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>special.WarProfiteer</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>War Profiteer</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>Kẻ trục lợi chiến tranh</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[9])</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[9])</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G157"/>
+  <autoFilter ref="A1:G160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11705,7 +11878,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[11])</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -11738,7 +11911,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:337 (Modules[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[1])</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -11777,7 +11950,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:351 (Modules[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[12])</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -11816,7 +11989,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:345 (Modules[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[6])</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -11855,7 +12028,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:356 (Modules[7])</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -11894,7 +12067,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:344 (Modules[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:354 (Modules[5])</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -11933,7 +12106,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:357 (Modules[8])</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -11972,7 +12145,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:349 (Modules[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[10])</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -12005,7 +12178,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Modules[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[0])</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -12047,7 +12220,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:340 (Modules[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[3])</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -12086,7 +12259,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:343 (Modules[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[4])</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -12125,7 +12298,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:352 (Modules[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[13])</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -12158,7 +12331,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:338 (Modules[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[2])</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -12191,7 +12364,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[9])</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -12299,7 +12472,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[24])</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12341,7 +12514,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[22])</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -12383,7 +12556,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[18])</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12425,7 +12598,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[31])</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12467,7 +12640,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:409 (Traits[37])</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12509,7 +12682,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[25])</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12551,7 +12724,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Traits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[3])</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12593,7 +12766,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:397 (Traits[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[35])</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -12635,7 +12808,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[42])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[42])</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -12677,7 +12850,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[38])</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -12719,7 +12892,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[21])</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -12761,7 +12934,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[34])</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -12803,7 +12976,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[43])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Traits[43])</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -12845,7 +13018,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:365 (Traits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[7])</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -12887,7 +13060,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[33])</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -12929,7 +13102,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[44])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[44])</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -12971,7 +13144,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:404 (Traits[41])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[41])</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -13013,7 +13186,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[20])</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -13055,7 +13228,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[15])</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -13097,7 +13270,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[11])</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -13139,7 +13312,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Traits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:369 (Traits[1])</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -13181,7 +13354,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[12])</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -13223,7 +13396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[40])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[40])</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -13265,7 +13438,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:364 (Traits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[6])</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -13307,7 +13480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[27])</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13349,7 +13522,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:363 (Traits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[5])</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -13391,7 +13564,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[14])</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13433,7 +13606,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[29])</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13475,7 +13648,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[13])</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -13517,7 +13690,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[23])</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -13559,7 +13732,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[32])</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -13601,7 +13774,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Traits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[2])</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -13643,7 +13816,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[36])</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13685,7 +13858,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[28])</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -13727,7 +13900,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Traits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[4])</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13769,7 +13942,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[26])</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13811,7 +13984,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[16])</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -13853,7 +14026,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:367 (Traits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[9])</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -13895,7 +14068,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[10])</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -13937,7 +14110,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:366 (Traits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[8])</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13979,7 +14152,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[39])</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -14021,7 +14194,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Traits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[0])</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14063,7 +14236,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:379 (Traits[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[19])</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14105,7 +14278,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[17])</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -14147,7 +14320,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[30])</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -14239,7 +14412,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[20])</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -14271,7 +14444,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[21])</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -14303,7 +14476,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Subs[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[5])</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -14335,7 +14508,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Subs[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[2])</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -14352,7 +14525,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên giáp cấp 3–4</t>
+          <t>+{percent}% sát thương lên xe nặng (lớp giáp thân xe 3–5, trúng mặt nào cũng tính)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -14367,7 +14540,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Subs[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[1])</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -14384,7 +14557,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>+{percent}% sát thương lên giáp cấp 0–2</t>
+          <t>+{percent}% sát thương lên xe nhẹ (lớp giáp thân xe 0–2)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -14399,7 +14572,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Subs[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[0])</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -14431,7 +14604,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Subs[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[3])</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -14463,7 +14636,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:417 (Subs[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[4])</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -14495,7 +14668,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[12])</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -14527,7 +14700,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[10])</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -14559,7 +14732,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[11])</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -14591,7 +14764,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:422 (Subs[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[9])</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -14623,7 +14796,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:419 (Subs[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[6])</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14655,7 +14828,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[22])</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14690,7 +14863,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[16])</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -14725,7 +14898,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[17])</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -14760,7 +14933,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[15])</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -14795,7 +14968,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[13])</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -14830,7 +15003,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[14])</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -14862,7 +15035,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[18])</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -14894,7 +15067,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:421 (Subs[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[8])</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -14926,7 +15099,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[19])</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -14958,7 +15131,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:420 (Subs[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[7])</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -15119,7 +15292,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:447 (Brands[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:458 (Brands[4])</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -15165,7 +15338,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[12])</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -15209,7 +15382,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:452 (Brands[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[9])</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -15246,16 +15419,16 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:449 (Brands[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[6])</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{"index":7,"id":"hivemind","stat":"SummonPower","value":0.15,"fourPiece":{"arg0":"SetSwarm","arg1":10}}</t>
+          <t>{"index":7,"id":"hivemind","stat":"SummonPower","value":0.1,"fourPiece":{"arg0":"SetSwarm","arg1":10}}</t>
         </is>
       </c>
     </row>
@@ -15291,7 +15464,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Brands[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[0])</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -15335,7 +15508,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Brands[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[1])</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -15376,7 +15549,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:446 (Brands[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[3])</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -15416,16 +15589,16 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[10])</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>{"index":11,"id":"phoenix","stat":"RepairReceived","value":0.1,"fourPiece":{"arg0":"SetPhoenix","arg1":0.1,"arg2":8}}</t>
+          <t>{"index":11,"id":"phoenix","stat":"RepairReceived","value":0.06,"fourPiece":{"arg0":"SetPhoenix","arg1":0.1,"arg2":8}}</t>
         </is>
       </c>
     </row>
@@ -15460,16 +15633,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:450 (Brands[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[7])</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>{"index":8,"id":"quartermaster","stat":"RepairReceived","value":0.1,"fourPiece":{"arg0":"SetSalvageRights","arg1":0.2,"arg2":0.1}}</t>
+          <t>{"index":8,"id":"quartermaster","stat":"RepairReceived","value":0.06,"fourPiece":{"arg0":"SetSalvageRights","arg1":0.2,"arg2":0.1}}</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15678,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:451 (Brands[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[8])</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -15549,7 +15722,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:448 (Brands[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[5])</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -15589,16 +15762,16 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Brands[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:456 (Brands[2])</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>{"index":3,"id":"vulcan","stat":"BurnDamage","value":0.25,"fourPiece":{"arg0":"SetFirestorm","arg1":0.1,"arg2":6}}</t>
+          <t>{"index":3,"id":"vulcan","stat":"BurnDamage","value":0.15,"fourPiece":{"arg0":"SetFirestorm","arg1":0.1,"arg2":6}}</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15821,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[11])</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -15810,7 +15983,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -15819,17 +15992,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.1;0.15;0.2;0.25;0.3</t>
+          <t>0.08;0.12;0.16;0.2;0.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:39 (TowerBases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:43 (TowerBases[13])</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>{"id":"ammo_handling","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Magazine","top":[0.1,0.15,0.2,0.25,0.3],"Main":"MagazineReload","MainScale":1.5}</t>
+          <t>{"id":"ammo_handling","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Magazine","top":[0.08,0.12,0.16,0.2,0.24],"Main":"MagazineReload","MainScale":1.25}</t>
         </is>
       </c>
     </row>
@@ -15866,17 +16039,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.08;0.12;0.16;0.2;0.25</t>
+          <t>0.06;0.09;0.12;0.15;0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:26 (TowerBases[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:27 (TowerBases[4])</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>{"id":"ammo_hoist","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"ProjectileSpeed","top":[0.08,0.12,0.16,0.2,0.25],"Main":"FireRate"}</t>
+          <t>{"id":"ammo_hoist","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"ProjectileSpeed","top":[0.06,0.09,0.12,0.15,0.18],"Main":"FireRate"}</t>
         </is>
       </c>
     </row>
@@ -15916,7 +16089,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:31 (TowerBases[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:32 (TowerBases[7])</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -15958,7 +16131,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:30 (TowerBases[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:31 (TowerBases[6])</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -16005,7 +16178,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:33 (TowerBases[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:34 (TowerBases[9])</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -16101,12 +16274,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>reinforced_concrete</t>
+          <t>grounding_mesh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bê tông cốt thép</t>
+          <t>Lưới tiếp địa năng lượng</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -16116,7 +16289,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ResistHighExplosive</t>
+          <t>ResistEnergy</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -16131,24 +16304,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:29 (TowerBases[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:36 (TowerBases[10])</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>{"id":"reinforced_concrete","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistHighExplosive","top":[0.04,0.06,0.09,0.12,0.15]}</t>
+          <t>{"id":"grounding_mesh","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistEnergy","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sabot_rounds</t>
+          <t>reinforced_concrete</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Đạn xuyên dưới cỡ</t>
+          <t>Bê tông cốt thép</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -16158,39 +16331,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Penetration</t>
+          <t>ResistHighExplosive</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>TowerWeapon</t>
+          <t>TowerStructure</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.4;0.55;0.7;0.85;1</t>
+          <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:23 (TowerBases[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:30 (TowerBases[5])</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>{"id":"sabot_rounds","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"Penetration","top":[0.4,0.55,0.7,0.85,1]}</t>
+          <t>{"id":"reinforced_concrete","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistHighExplosive","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>search_radar</t>
+          <t>sabot_rounds</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Radar tìm kiếm</t>
+          <t>Đạn xuyên dưới cỡ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -16200,39 +16373,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SpreadLong</t>
+          <t>Penetration</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>TowerSystems</t>
+          <t>TowerWeapon</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.08;0.12;0.16;0.2;0.25</t>
+          <t>0.4;0.55;0.7;0.85;1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:36 (TowerBases[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:23 (TowerBases[1])</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>{"id":"search_radar","slot":"TowerSystems","branches":"NoBranch","implicitStat":"SpreadLong","top":[0.08,0.12,0.16,0.2,0.25]}</t>
+          <t>{"id":"sabot_rounds","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"Penetration","top":[0.4,0.55,0.7,0.85,1]}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>slat_screens</t>
+          <t>search_radar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lưới chắn rốc-két</t>
+          <t>Radar tìm kiếm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -16242,85 +16415,127 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ResistRocket</t>
-        </is>
-      </c>
-      <c r="G13" t="b">
-        <v>1</v>
+          <t>SpreadLong</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>TowerStructure</t>
+          <t>TowerSystems</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.06;0.09;0.13;0.17;0.22</t>
+          <t>0.08;0.12;0.16;0.2;0.25</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:32 (TowerBases[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:39 (TowerBases[11])</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>{"id":"slat_screens","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistRocket","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
+          <t>{"id":"search_radar","slot":"TowerSystems","branches":"NoBranch","implicitStat":"SpreadLong","top":[0.08,0.12,0.16,0.2,0.25]}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>slat_screens</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lưới chắn rốc-két</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NoBranch</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ResistRocket</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TowerStructure</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.06;0.09;0.13;0.17;0.22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:33 (TowerBases[8])</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{"id":"slat_screens","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistRocket","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>traverse_motors</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Mô-tơ xoay tháp</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>TurretRate</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>1.5</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>TowerSystems</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:37 (TowerBases[11])</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:40 (TowerBases[12])</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>{"id":"traverse_motors","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Spread","top":[0.04,0.06,0.09,0.12,0.15],"Main":"TurretRate","MainScale":1.5}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K14"/>
+  <autoFilter ref="A1:K15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16430,7 +16645,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[6])</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -16472,7 +16687,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:58 (TowerTraits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[5])</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -16519,7 +16734,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:52 (TowerTraits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[1])</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -16566,7 +16781,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[9])</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -16613,7 +16828,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:53 (TowerTraits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[2])</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -16660,7 +16875,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[8])</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -16702,7 +16917,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:65 (TowerTraits[7])</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -16749,7 +16964,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:51 (TowerTraits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[0])</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -16791,7 +17006,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[3])</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -16836,7 +17051,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[4])</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -16907,7 +17122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:491 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16930,7 +17145,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:490 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:501 (BuildCaps)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -16953,7 +17168,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:510 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:521 (BuildCaps)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -16976,7 +17191,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:505 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:516 (BuildCaps)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -16999,7 +17214,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:494 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:505 (BuildCaps)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -17022,7 +17237,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:495 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:506 (BuildCaps)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -17045,7 +17260,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:470 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:481 (BuildCaps)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -17068,7 +17283,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:513 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:524 (BuildCaps)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -17091,7 +17306,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:475 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -17114,7 +17329,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:478 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:489 (BuildCaps)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -17137,7 +17352,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:514 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:525 (BuildCaps)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -17160,7 +17375,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:477 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:488 (BuildCaps)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -17183,7 +17398,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:476 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:487 (BuildCaps)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -17206,7 +17421,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:479 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:490 (BuildCaps)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -17229,7 +17444,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:471 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:482 (BuildCaps)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -17252,7 +17467,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:472 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:483 (BuildCaps)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -17275,7 +17490,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:517 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:528 (BuildCaps)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -17298,7 +17513,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:516 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:527 (BuildCaps)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -17321,7 +17536,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:484 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:495 (BuildCaps)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -17344,7 +17559,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:485 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:496 (BuildCaps)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17367,7 +17582,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:489 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:500 (BuildCaps)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17390,7 +17605,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:483 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:494 (BuildCaps)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17413,7 +17628,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:480 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:491 (BuildCaps)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17436,7 +17651,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:474 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:485 (BuildCaps)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17459,7 +17674,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:506 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:517 (BuildCaps)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17482,7 +17697,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:512 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:523 (BuildCaps)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17505,7 +17720,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:519 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:530 (BuildCaps)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17528,7 +17743,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:488 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:499 (BuildCaps)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17551,7 +17766,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17574,7 +17789,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17597,7 +17812,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:513 (BuildCaps)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -17620,7 +17835,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -17643,7 +17858,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:500 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:511 (BuildCaps)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -17666,7 +17881,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -17689,7 +17904,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:501 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:512 (BuildCaps)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -17712,7 +17927,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:499 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:510 (BuildCaps)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -17735,7 +17950,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -17758,7 +17973,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:518 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:529 (BuildCaps)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -17781,7 +17996,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:498 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:509 (BuildCaps)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -17804,7 +18019,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:508 (BuildCaps)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -17827,7 +18042,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:515 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:526 (BuildCaps)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -17850,7 +18065,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:473 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:484 (BuildCaps)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -17873,7 +18088,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:496 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:507 (BuildCaps)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -17896,7 +18111,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:482 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:493 (BuildCaps)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -17919,7 +18134,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:508 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:519 (BuildCaps)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -17942,7 +18157,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:509 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:520 (BuildCaps)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -17965,7 +18180,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:507 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:518 (BuildCaps)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -17988,7 +18203,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:504 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:515 (BuildCaps)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -18011,7 +18226,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:511 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:522 (BuildCaps)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -18034,7 +18249,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:503 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:514 (BuildCaps)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -18057,7 +18272,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:492 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:503 (BuildCaps)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -18080,7 +18295,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:493 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:504 (BuildCaps)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -18103,7 +18318,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:481 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:492 (BuildCaps)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Docs/export/current/10_trang_bi.xlsx
+++ b/Docs/export/current/10_trang_bi.xlsx
@@ -29,7 +29,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trang_bi_dac_tinh'!$A$1:$H$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trang_bi_dong_phu'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Trang_bi_bo'!$A$1:$P$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trang_bi_thap'!$A$1:$K$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Trang_bi_thap'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Trang_bi_dac_tinh_thap'!$A$1:$J$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Trang_bi_tran'!$A$1:$E$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Trang_bi_chi_so'!$A$1:$F$28</definedName>
@@ -628,7 +628,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:290 (Bases[16])</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:294 (Bases[18])</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:330 (Bases[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:335 (Bases[37])</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:334 (Bases[36])</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:287 (Bases[14])</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:321 (Bases[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:326 (Bases[31])</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:310 (Bases[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:313 (Bases[26])</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:300 (Bases[20])</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:324 (Bases[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[33])</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[32])</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:291 (Bases[17])</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:305 (Bases[22])</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:328 (Bases[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:333 (Bases[35])</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1295,6 +1295,9 @@
           <t>FireRate</t>
         </is>
       </c>
+      <c r="G21" t="n">
+        <v>0.25</v>
+      </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -1315,17 +1318,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0;0;0.08;0.1;0.12</t>
+          <t>0;0;0.06;0.0725;0.075</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:281 (Bases[12])</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>{"id":"hair_trigger","slot":"Loader","implicitStat":"FireRate","top":[0,0,0.08,0.1,0.12],"Penalty":"Spread","PenaltyTop":[0,0,-0.08,-0.1,-0.12],"MinRarity":2}</t>
+          <t>{"id":"hair_trigger","slot":"Loader","implicitStat":"FireRate","top":[0,0,0.06,0.0725,0.075],"Penalty":"Spread","PenaltyTop":[0,0,-0.08,-0.1,-0.12],"MinRarity":2,"MainScale":0.25}</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1447,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[34])</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -1487,7 +1490,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Bases[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:341 (Bases[39])</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -1550,7 +1553,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.8</v>
+        <v>1.7142857</v>
       </c>
       <c r="H27" t="n">
         <v>2</v>
@@ -1580,12 +1583,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:293 (Bases[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:296 (Bases[19])</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>{"id":"monolith_plate","slot":"Armor","implicitStat":"Count","top":[0,0,0,0,0],"Penalty":"Speed","PenaltyTop":[0,0,-0.04,-0.05,-0.06],"MinRarity":2,"MainScale":1.8,"NoSubs":true}</t>
+          <t>{"id":"monolith_plate","slot":"Armor","implicitStat":"Count","top":[0,0,0,0,0],"Penalty":"Speed","PenaltyTop":[0,0,-0.04,-0.05,-0.06],"MinRarity":2,"MainScale":1.7142857,"NoSubs":true}</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1623,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:304 (Bases[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:307 (Bases[24])</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -1645,6 +1648,9 @@
           <t>Speed</t>
         </is>
       </c>
+      <c r="G29" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H29" t="n">
         <v>2</v>
       </c>
@@ -1665,17 +1671,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>0;0;0.08;0.1;0.12</t>
+          <t>0;0;0.055;0.0675;0.08</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:319 (Bases[28])</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>{"id":"overtuned_engine","slot":"Engine","implicitStat":"Speed","top":[0,0,0.08,0.1,0.12],"Penalty":"Health","PenaltyTop":[0,0,-0.03,-0.04,-0.05],"MinRarity":2}</t>
+          <t>{"id":"overtuned_engine","slot":"Engine","implicitStat":"Speed","top":[0,0,0.055,0.0675,0.08],"Penalty":"Health","PenaltyTop":[0,0,-0.03,-0.04,-0.05],"MinRarity":2,"MainScale":0.5}</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1750,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[21])</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -1781,7 +1787,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[29])</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -1865,7 +1871,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:337 (Bases[38])</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -1905,7 +1911,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[23])</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -1942,7 +1948,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[15])</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -1982,7 +1988,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:284 (Bases[13])</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -2019,7 +2025,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:325 (Bases[30])</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -2056,7 +2062,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:315 (Bases[27])</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -2133,7 +2139,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:309 (Bases[25])</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -5645,7 +5651,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:458 (Brands[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[4])</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -5678,7 +5684,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:473 (Brands[12])</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -5711,7 +5717,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[9])</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -5744,7 +5750,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[6])</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -5777,7 +5783,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[0])</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -5810,7 +5816,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[1])</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -5843,7 +5849,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[3])</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -5876,7 +5882,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:470 (Brands[10])</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -5909,7 +5915,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[7])</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -5942,7 +5948,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:467 (Brands[8])</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -5975,7 +5981,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:464 (Brands[5])</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -6008,7 +6014,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:456 (Brands[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[2])</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -6041,7 +6047,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:471 (Brands[11])</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -6107,7 +6113,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:290 (Bases[16])</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -6140,7 +6146,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:292 (Bases[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:294 (Bases[18])</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -6239,7 +6245,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:330 (Bases[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:335 (Bases[37])</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -6305,7 +6311,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:334 (Bases[36])</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -6338,7 +6344,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:285 (Bases[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:287 (Bases[14])</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -6371,7 +6377,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:321 (Bases[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:326 (Bases[31])</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -6404,7 +6410,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:310 (Bases[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:313 (Bases[26])</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -6437,7 +6443,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:297 (Bases[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:300 (Bases[20])</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -6503,7 +6509,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:324 (Bases[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:329 (Bases[33])</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -6536,7 +6542,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[32])</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -6569,7 +6575,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:289 (Bases[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:291 (Bases[17])</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -6635,7 +6641,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:305 (Bases[22])</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -6668,7 +6674,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:328 (Bases[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:333 (Bases[35])</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -6701,7 +6707,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:279 (Bases[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:281 (Bases[12])</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -6800,7 +6806,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:327 (Bases[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[34])</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -6833,7 +6839,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:336 (Bases[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:341 (Bases[39])</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -6899,7 +6905,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:293 (Bases[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:296 (Bases[19])</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -6932,7 +6938,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:304 (Bases[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:307 (Bases[24])</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -6965,7 +6971,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:314 (Bases[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:319 (Bases[28])</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -7031,7 +7037,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:299 (Bases[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:302 (Bases[21])</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -7064,7 +7070,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:317 (Bases[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:322 (Bases[29])</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -7130,7 +7136,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:332 (Bases[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:337 (Bases[38])</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -7163,7 +7169,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:303 (Bases[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[23])</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -7196,7 +7202,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:286 (Bases[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:288 (Bases[15])</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -7229,7 +7235,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:282 (Bases[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:284 (Bases[13])</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -7262,7 +7268,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:320 (Bases[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:325 (Bases[30])</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -7295,7 +7301,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:312 (Bases[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:315 (Bases[27])</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -7361,7 +7367,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:306 (Bases[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:309 (Bases[25])</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -7427,7 +7433,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:43 (TowerBases[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:44 (TowerBases[13])</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -7856,7 +7862,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[24])</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -7889,7 +7895,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:397 (Traits[22])</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7922,7 +7928,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[18])</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7955,7 +7961,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[31])</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7988,7 +7994,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:409 (Traits[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[37])</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8021,7 +8027,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[25])</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8054,7 +8060,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[3])</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8087,7 +8093,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[35])</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -8120,7 +8126,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[42])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:420 (Traits[42])</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -8153,7 +8159,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[38])</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -8186,7 +8192,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[21])</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8219,7 +8225,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:411 (Traits[34])</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8252,7 +8258,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Traits[43])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:421 (Traits[43])</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -8285,7 +8291,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[7])</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8318,7 +8324,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[33])</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8351,7 +8357,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[44])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Traits[44])</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8384,7 +8390,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[41])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:419 (Traits[41])</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8417,7 +8423,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[20])</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8450,7 +8456,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[15])</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8483,7 +8489,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[11])</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8516,7 +8522,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:369 (Traits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[1])</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8549,7 +8555,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[12])</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8582,7 +8588,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[40])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[40])</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8615,7 +8621,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:379 (Traits[6])</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8648,7 +8654,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[27])</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -8681,7 +8687,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[5])</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -8714,7 +8720,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[14])</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -8747,7 +8753,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[29])</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -8780,7 +8786,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:387 (Traits[13])</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -8813,7 +8819,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[23])</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -8846,7 +8852,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[32])</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -8879,7 +8885,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[2])</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -8912,7 +8918,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[36])</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -8945,7 +8951,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:404 (Traits[28])</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -8978,7 +8984,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[4])</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -9011,7 +9017,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[26])</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -9044,7 +9050,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[16])</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -9077,7 +9083,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[9])</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -9110,7 +9116,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[10])</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -9143,7 +9149,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[8])</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -9176,7 +9182,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:417 (Traits[39])</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -9209,7 +9215,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[0])</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -9242,7 +9248,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[19])</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -9275,7 +9281,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[17])</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -9308,7 +9314,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[30])</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -9341,7 +9347,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:64 (TowerTraits[6])</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -9374,7 +9380,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[5])</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -9407,7 +9413,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[1])</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -9440,7 +9446,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:68 (TowerTraits[9])</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -9473,7 +9479,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:58 (TowerTraits[2])</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -9506,7 +9512,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[8])</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -9539,7 +9545,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:65 (TowerTraits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[7])</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -9572,7 +9578,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[0])</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -9605,7 +9611,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:60 (TowerTraits[3])</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -9638,7 +9644,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[4])</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -9671,7 +9677,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:448 (Subs[20])</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -9704,7 +9710,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:449 (Subs[21])</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -9737,7 +9743,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[5])</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -9770,7 +9776,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[2])</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -9803,7 +9809,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[1])</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -9836,7 +9842,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[0])</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -9869,7 +9875,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[3])</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -9902,7 +9908,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[4])</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -9935,7 +9941,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[12])</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -9968,7 +9974,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[10])</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -10001,7 +10007,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[11])</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -10034,7 +10040,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[9])</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -10067,7 +10073,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[6])</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -10100,7 +10106,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:450 (Subs[22])</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -10133,7 +10139,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[16])</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -10166,7 +10172,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[17])</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -10199,7 +10205,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[15])</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -10232,7 +10238,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[13])</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -10265,7 +10271,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[14])</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -10298,7 +10304,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:446 (Subs[18])</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -10331,7 +10337,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[8])</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -10364,7 +10370,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:447 (Subs[19])</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -10397,7 +10403,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[7])</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -10430,7 +10436,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:365 (Modules[11])</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -10463,7 +10469,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:352 (Modules[1])</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -10496,7 +10502,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:366 (Modules[12])</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -10529,7 +10535,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[6])</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -10562,7 +10568,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:356 (Modules[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[7])</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>
@@ -10595,7 +10601,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:354 (Modules[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[5])</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -10628,7 +10634,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:357 (Modules[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[8])</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -10661,7 +10667,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:364 (Modules[10])</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -10694,7 +10700,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:351 (Modules[0])</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -10727,7 +10733,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[3])</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -10760,7 +10766,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[4])</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
@@ -10793,7 +10799,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:367 (Modules[13])</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
@@ -10826,7 +10832,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[2])</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -10859,7 +10865,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:363 (Modules[9])</t>
         </is>
       </c>
       <c r="G160" t="inlineStr"/>
@@ -11135,7 +11141,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:486 (GoldGuaranteed[0])</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -11163,7 +11169,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:486 (GoldGuaranteed[1])</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -11191,7 +11197,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:486 (GoldGuaranteed[2])</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11219,7 +11225,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:486 (GoldGuaranteed[3])</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -11247,7 +11253,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:429 (GoldGuaranteed[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:486 (GoldGuaranteed[4])</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -11275,7 +11281,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:487 (LegendaryGuaranteed[0])</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -11303,7 +11309,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:487 (LegendaryGuaranteed[1])</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -11331,7 +11337,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:487 (LegendaryGuaranteed[2])</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -11359,7 +11365,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:487 (LegendaryGuaranteed[3])</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11387,7 +11393,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:430 (LegendaryGuaranteed[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/Arsenal.cs:487 (LegendaryGuaranteed[4])</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -11878,7 +11884,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:365 (Modules[11])</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -11911,7 +11917,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:347 (Modules[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:352 (Modules[1])</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -11950,7 +11956,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:366 (Modules[12])</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -11989,7 +11995,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:360 (Modules[6])</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -12028,7 +12034,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:356 (Modules[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:361 (Modules[7])</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -12067,7 +12073,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:354 (Modules[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[5])</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -12106,7 +12112,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:357 (Modules[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[8])</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -12145,7 +12151,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:359 (Modules[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:364 (Modules[10])</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -12178,7 +12184,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:346 (Modules[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:351 (Modules[0])</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -12220,7 +12226,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:350 (Modules[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:355 (Modules[3])</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -12259,7 +12265,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[4])</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -12298,7 +12304,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:362 (Modules[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:367 (Modules[13])</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -12331,7 +12337,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:348 (Modules[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:353 (Modules[2])</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -12364,7 +12370,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:358 (Modules[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:363 (Modules[9])</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -12472,7 +12478,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[24])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[24])</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -12514,7 +12520,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:392 (Traits[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:397 (Traits[22])</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -12556,7 +12562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[18])</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -12598,7 +12604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:402 (Traits[31])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[31])</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12640,7 +12646,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:409 (Traits[37])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[37])</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12682,7 +12688,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[25])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[25])</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12724,7 +12730,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:371 (Traits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[3])</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12766,7 +12772,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:407 (Traits[35])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[35])</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -12808,7 +12814,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[42])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:420 (Traits[42])</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -12850,7 +12856,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[38])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:415 (Traits[38])</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -12892,7 +12898,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[21])</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -12934,7 +12940,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[34])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:411 (Traits[34])</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -12976,7 +12982,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:416 (Traits[43])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:421 (Traits[43])</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -13018,7 +13024,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[7])</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -13060,7 +13066,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[33])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:410 (Traits[33])</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -13102,7 +13108,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[44])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Traits[44])</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -13144,7 +13150,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:414 (Traits[41])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:419 (Traits[41])</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -13186,7 +13192,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:395 (Traits[20])</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -13228,7 +13234,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:384 (Traits[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[15])</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -13270,7 +13276,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:380 (Traits[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[11])</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -13312,7 +13318,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:369 (Traits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[1])</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -13354,7 +13360,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[12])</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -13396,7 +13402,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[40])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:418 (Traits[40])</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -13438,7 +13444,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:374 (Traits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:379 (Traits[6])</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -13480,7 +13486,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[27])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[27])</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -13522,7 +13528,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[5])</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -13564,7 +13570,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:388 (Traits[14])</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -13606,7 +13612,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:400 (Traits[29])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:405 (Traits[29])</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -13648,7 +13654,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:387 (Traits[13])</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -13690,7 +13696,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:393 (Traits[23])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:398 (Traits[23])</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -13732,7 +13738,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:403 (Traits[32])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[32])</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -13774,7 +13780,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:370 (Traits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:375 (Traits[2])</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -13816,7 +13822,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:408 (Traits[36])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:413 (Traits[36])</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13858,7 +13864,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:399 (Traits[28])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:404 (Traits[28])</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -13900,7 +13906,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:372 (Traits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[4])</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -13942,7 +13948,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:396 (Traits[26])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[26])</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13984,7 +13990,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:385 (Traits[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:390 (Traits[16])</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -14026,7 +14032,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:377 (Traits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:382 (Traits[9])</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -14068,7 +14074,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:378 (Traits[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:383 (Traits[10])</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -14110,7 +14116,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:376 (Traits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:381 (Traits[8])</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -14152,7 +14158,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:412 (Traits[39])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:417 (Traits[39])</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -14194,7 +14200,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:368 (Traits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:373 (Traits[0])</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -14236,7 +14242,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:389 (Traits[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:394 (Traits[19])</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14278,7 +14284,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:386 (Traits[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:391 (Traits[17])</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -14320,7 +14326,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:401 (Traits[30])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:406 (Traits[30])</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -14412,7 +14418,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[20])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:448 (Subs[20])</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -14444,7 +14450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[21])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:449 (Subs[21])</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -14476,7 +14482,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[5])</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -14508,7 +14514,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:425 (Subs[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[2])</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -14540,7 +14546,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:424 (Subs[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[1])</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -14572,7 +14578,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:423 (Subs[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:428 (Subs[0])</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -14604,7 +14610,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:426 (Subs[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[3])</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -14636,7 +14642,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:427 (Subs[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[4])</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -14668,7 +14674,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[12])</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -14700,7 +14706,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:433 (Subs[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[10])</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -14732,7 +14738,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[11])</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -14764,7 +14770,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:432 (Subs[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[9])</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -14796,7 +14802,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:429 (Subs[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:434 (Subs[6])</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14828,7 +14834,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[22])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:450 (Subs[22])</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14863,7 +14869,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:439 (Subs[16])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:444 (Subs[16])</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -14898,7 +14904,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:440 (Subs[17])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:445 (Subs[17])</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -14933,7 +14939,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:438 (Subs[15])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:443 (Subs[15])</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -14968,7 +14974,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[13])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[13])</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -15003,7 +15009,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:437 (Subs[14])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[14])</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -15035,7 +15041,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:441 (Subs[18])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:446 (Subs[18])</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -15067,7 +15073,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:431 (Subs[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:436 (Subs[8])</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -15099,7 +15105,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:442 (Subs[19])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:447 (Subs[19])</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -15131,7 +15137,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:430 (Subs[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:435 (Subs[7])</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -15292,7 +15298,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:458 (Brands[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[4])</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -15338,7 +15344,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[12])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:473 (Brands[12])</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -15382,7 +15388,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:463 (Brands[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:468 (Brands[9])</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -15423,7 +15429,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[6])</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -15464,7 +15470,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:454 (Brands[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[0])</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -15508,7 +15514,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:455 (Brands[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:460 (Brands[1])</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -15549,7 +15555,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:457 (Brands[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[3])</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -15593,7 +15599,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:465 (Brands[10])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:470 (Brands[10])</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -15637,7 +15643,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[7])</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -15678,7 +15684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:462 (Brands[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:467 (Brands[8])</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -15722,7 +15728,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:459 (Brands[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:464 (Brands[5])</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -15766,7 +15772,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:456 (Brands[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:461 (Brands[2])</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -15821,7 +15827,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:466 (Brands[11])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:471 (Brands[11])</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -15847,14 +15853,16 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15875,40 +15883,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>implicit2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>implicit_stat</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>main_scale</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>plating</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>top</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>top2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>nguon</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>raw_json</t>
         </is>
@@ -15930,27 +15948,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Splash</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>TowerWeapon</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.05;0.08;0.12;0.16;0.2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:25 (TowerBases[3])</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>{"id":"airburst_shells","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"Splash","top":[0.05,0.08,0.12,0.16,0.2]}</t>
         </is>
@@ -15974,35 +15992,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>MagazineReload</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Magazine</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>MagazineReload</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>TowerSystems</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.08;0.12;0.16;0.2;0.24</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:43 (TowerBases[13])</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>{"id":"ammo_handling","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Magazine","top":[0.08,0.12,0.16,0.2,0.24],"Main":"MagazineReload","MainScale":1.25}</t>
+          <t>0.07;0.1;0.12;0.14;0.16</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:44 (TowerBases[13])</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>{"id":"ammo_handling","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Magazine","top":[0.08,0.12,0.16,0.2,0.24],"Main":"MagazineReload","Implicit2":"MagazineReload","Top2":[0.07,0.1,0.12,0.14,0.16]}</t>
         </is>
       </c>
     </row>
@@ -16022,32 +16047,32 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ProjectileSpeed</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>FireRate</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>TowerWeapon</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.06;0.09;0.12;0.15;0.18</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:27 (TowerBases[4])</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>{"id":"ammo_hoist","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"ProjectileSpeed","top":[0.06,0.09,0.12,0.15,0.18],"Main":"FireRate"}</t>
         </is>
@@ -16069,30 +16094,30 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>ResistIndirect</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.06;0.09;0.13;0.17;0.22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:32 (TowerBases[7])</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>{"id":"blast_walls","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistIndirect","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
         </is>
@@ -16114,27 +16139,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>ResistShapedCharge</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:31 (TowerBases[6])</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>{"id":"composite_casemate","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistShapedCharge","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
@@ -16156,32 +16181,32 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>RegenDelay</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Regen</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>1;1.5;2;2.5;3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:34 (TowerBases[9])</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>{"id":"engineer_bay","slot":"TowerStructure","branches":"NoBranch","implicitStat":"RegenDelay","top":[1,1.5,2,2.5,3],"Main":"Regen"}</t>
         </is>
@@ -16203,27 +16228,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>DamageVsAir</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>TowerWeapon</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0.05;0.08;0.12;0.16;0.2</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:24 (TowerBases[2])</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>{"id":"flak_proximity_fuze","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"DamageVsAir","top":[0.05,0.08,0.12,0.16,0.2]}</t>
         </is>
@@ -16245,27 +16270,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>TowerWeapon</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.02;0.03;0.04;0.06;0.08</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:21 (TowerBases[0])</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>{"id":"fortress_barrel","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"Range","top":[0.02,0.03,0.04,0.06,0.08]}</t>
         </is>
@@ -16287,27 +16312,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>ResistEnergy</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:36 (TowerBases[10])</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>{"id":"grounding_mesh","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistEnergy","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
@@ -16329,27 +16354,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>ResistHighExplosive</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:30 (TowerBases[5])</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>{"id":"reinforced_concrete","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistHighExplosive","top":[0.04,0.06,0.09,0.12,0.15]}</t>
         </is>
@@ -16371,27 +16396,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Penetration</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>TowerWeapon</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>0.4;0.55;0.7;0.85;1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:23 (TowerBases[1])</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>{"id":"sabot_rounds","slot":"TowerWeapon","branches":"NoBranch","implicitStat":"Penetration","top":[0.4,0.55,0.7,0.85,1]}</t>
         </is>
@@ -16413,27 +16438,27 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>SpreadLong</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>TowerSystems</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>0.08;0.12;0.16;0.2;0.25</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:39 (TowerBases[11])</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>{"id":"search_radar","slot":"TowerSystems","branches":"NoBranch","implicitStat":"SpreadLong","top":[0.08,0.12,0.16,0.2,0.25]}</t>
         </is>
@@ -16455,30 +16480,30 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>ResistRocket</t>
         </is>
       </c>
-      <c r="G14" t="b">
+      <c r="H14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>TowerStructure</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0.06;0.09;0.13;0.17;0.22</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:33 (TowerBases[8])</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>{"id":"slat_screens","slot":"TowerStructure","branches":"NoBranch","implicitStat":"ResistRocket","top":[0.06,0.09,0.13,0.17,0.22],"Plating":true}</t>
         </is>
@@ -16500,42 +16525,42 @@
           <t>NoBranch</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>TurretRate</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>1.5</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>TowerSystems</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>0.04;0.06;0.09;0.12;0.15</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:40 (TowerBases[12])</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>{"id":"traverse_motors","slot":"TowerSystems","branches":"NoBranch","implicitStat":"Spread","top":[0.04,0.06,0.09,0.12,0.15],"Main":"TurretRate","MainScale":1.5}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K15"/>
+  <autoFilter ref="A1:M15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16645,7 +16670,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[6])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:64 (TowerTraits[6])</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -16687,7 +16712,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[5])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:63 (TowerTraits[5])</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -16734,7 +16759,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[1])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[1])</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -16781,7 +16806,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[9])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:68 (TowerTraits[9])</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -16828,7 +16853,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:57 (TowerTraits[2])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:58 (TowerTraits[2])</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -16875,7 +16900,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[8])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:67 (TowerTraits[8])</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -16917,7 +16942,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:65 (TowerTraits[7])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:66 (TowerTraits[7])</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -16964,7 +16989,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:55 (TowerTraits[0])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:56 (TowerTraits[0])</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -17006,7 +17031,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:59 (TowerTraits[3])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:60 (TowerTraits[3])</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -17051,7 +17076,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:61 (TowerTraits[4])</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.Tower.cs:62 (TowerTraits[4])</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -17122,7 +17147,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:507 (BuildCaps)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17145,7 +17170,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:501 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:506 (BuildCaps)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17168,7 +17193,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:521 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:526 (BuildCaps)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -17191,7 +17216,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:516 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:521 (BuildCaps)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -17214,7 +17239,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:505 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:510 (BuildCaps)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -17237,7 +17262,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:506 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:511 (BuildCaps)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -17260,7 +17285,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:481 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -17283,7 +17308,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:524 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:529 (BuildCaps)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -17306,7 +17331,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:486 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:491 (BuildCaps)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -17329,7 +17354,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:489 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:494 (BuildCaps)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -17352,7 +17377,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:525 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:530 (BuildCaps)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -17375,7 +17400,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:488 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:493 (BuildCaps)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -17398,7 +17423,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:487 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:492 (BuildCaps)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -17421,7 +17446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:490 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:495 (BuildCaps)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -17444,7 +17469,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:482 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:487 (BuildCaps)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -17467,7 +17492,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:483 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:488 (BuildCaps)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -17490,7 +17515,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:528 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:533 (BuildCaps)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -17513,7 +17538,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:527 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:532 (BuildCaps)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -17536,7 +17561,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:495 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:500 (BuildCaps)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -17559,7 +17584,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:496 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:501 (BuildCaps)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -17582,7 +17607,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:500 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:505 (BuildCaps)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -17605,7 +17630,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:494 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:499 (BuildCaps)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -17628,7 +17653,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:491 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:496 (BuildCaps)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -17651,7 +17676,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:485 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:490 (BuildCaps)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -17674,7 +17699,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:517 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:522 (BuildCaps)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -17697,7 +17722,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:523 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:528 (BuildCaps)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -17720,7 +17745,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:530 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:535 (BuildCaps)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -17743,7 +17768,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:499 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:504 (BuildCaps)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -17766,7 +17791,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -17789,7 +17814,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -17812,7 +17837,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:513 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:518 (BuildCaps)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -17835,7 +17860,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -17858,7 +17883,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:511 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:516 (BuildCaps)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -17881,7 +17906,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -17904,7 +17929,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:512 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:517 (BuildCaps)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -17927,7 +17952,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:510 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:515 (BuildCaps)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -17950,7 +17975,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:502 (BuildCaps)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -17973,7 +17998,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:529 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:534 (BuildCaps)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -17996,7 +18021,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:509 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:514 (BuildCaps)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -18019,7 +18044,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:508 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:513 (BuildCaps)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -18042,7 +18067,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:526 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:531 (BuildCaps)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -18065,7 +18090,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:484 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:489 (BuildCaps)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -18088,7 +18113,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:507 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:512 (BuildCaps)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -18111,7 +18136,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:493 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:498 (BuildCaps)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -18134,7 +18159,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:519 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:524 (BuildCaps)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -18157,7 +18182,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:520 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:525 (BuildCaps)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -18180,7 +18205,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:518 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:523 (BuildCaps)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -18203,7 +18228,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:515 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:520 (BuildCaps)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -18226,7 +18251,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:522 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:527 (BuildCaps)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -18249,7 +18274,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:514 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:519 (BuildCaps)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -18272,7 +18297,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:503 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:508 (BuildCaps)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -18295,7 +18320,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:504 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:509 (BuildCaps)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -18318,7 +18343,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:492 (BuildCaps)</t>
+          <t>Assets/MachineBrigade/Scripts/Game/Match/GearCatalog.cs:497 (BuildCaps)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">

--- a/Docs/export/current/10_trang_bi.xlsx
+++ b/Docs/export/current/10_trang_bi.xlsx
@@ -1485,7 +1485,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6;6.5;7;7.5;8</t>
+          <t>6.0;6.5;7.0;7.5;8.0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>{"id":"laser_warning","slot":"Optics","implicitStat":"LaserWarning","top":[6,6.5,7,7.5,8],"Flat":true,"Hidden":true}</t>
+          <t>{"id":"laser_warning","slot":"Optics","implicitStat":"LaserWarning","top":[6.0,6.5,7.0,7.5,8.0],"Flat":true,"Hidden":true}</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1;1.5;2;2.5;3</t>
+          <t>1;1.5;2.0;2.5;3.0</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>{"id":"toolbox","slot":"Repair","implicitStat":"RegenDelay","top":[1,1.5,2,2.5,3]}</t>
+          <t>{"id":"toolbox","slot":"Repair","implicitStat":"RegenDelay","top":[1,1.5,2.0,2.5,3.0]}</t>
         </is>
       </c>
     </row>
@@ -12117,7 +12117,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"module":"MineDispenser","need":"Ground","epic":2,"legendary":3,"epic2":20,"legendary2":15}</t>
+          <t>{"module":"MineDispenser","need":"Ground","epic":2.0,"legendary":3.0,"epic2":20.0,"legendary2":15.0}</t>
         </is>
       </c>
     </row>
@@ -12396,8 +12396,8 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -12547,12 +12547,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.1;20</t>
+          <t>0.1;20.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.15;16</t>
+          <t>0.15;16.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>{"id":"AegisBarrier","slot":"Armor","branches":"Any","epic":[0.1,20],"legendary":[0.15,16]}</t>
+          <t>{"id":"AegisBarrier","slot":"Armor","branches":"Any","epic":[0.1,20.0],"legendary":[0.15,16.0]}</t>
         </is>
       </c>
     </row>
@@ -12673,12 +12673,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>{"id":"AngledGlacis","slot":"Armor","branches":"Ground","epic":[6],"legendary":[5]}</t>
+          <t>{"id":"AngledGlacis","slot":"Armor","branches":"Ground","epic":[6.0],"legendary":[5.0]}</t>
         </is>
       </c>
     </row>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.15;80;5</t>
+          <t>0.15;80.0;5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.25;100;8</t>
+          <t>0.25;100.0;8.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>{"id":"CounterBatteryRadar","slot":"Optics","branches":"Any","epic":[0.15,80,5],"legendary":[0.25,100,8]}</t>
+          <t>{"id":"CounterBatteryRadar","slot":"Optics","branches":"Any","epic":[0.15,80.0,5.0],"legendary":[0.25,100.0,8.0]}</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>{"id":"DamageControl","slot":"Repair","branches":"Any","epic":[15],"legendary":[10]}</t>
+          <t>{"id":"DamageControl","slot":"Repair","branches":"Any","epic":[15.0],"legendary":[10.0]}</t>
         </is>
       </c>
     </row>
@@ -13681,12 +13681,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3;20</t>
+          <t>3.0;20.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4;15</t>
+          <t>4.0;15.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -13701,7 +13701,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>{"id":"ReactiveBlocks","slot":"Armor","branches":"Ground","epic":[3,20],"legendary":[4,15]}</t>
+          <t>{"id":"ReactiveBlocks","slot":"Armor","branches":"Ground","epic":[3.0,20.0],"legendary":[4.0,15.0]}</t>
         </is>
       </c>
     </row>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{"index":5,"id":"aegis","stat":"DamageTaken","value":0.05,"fourPiece":{"arg0":"SetSharedShield","arg1":0.12,"arg2":25,"arg3":12}}</t>
+          <t>{"index":5,"id":"aegis","stat":"DamageTaken","value":0.05,"fourPiece":{"arg0":"SetSharedShield","arg1":0.12,"arg2":25.0,"arg3":12.0}}</t>
         </is>
       </c>
     </row>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{"index":"BulwarkBrand","id":"bulwark","stat":"Health","value":0.1,"fourPiece":{"arg0":"SetBulwarkPost","arg1":20},"TowerOnly":true}</t>
+          <t>{"index":"BulwarkBrand","id":"bulwark","stat":"Health","value":0.1,"fourPiece":{"arg0":"SetBulwarkPost","arg1":20.0},"TowerOnly":true}</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{"index":10,"id":"hammerfall","stat":"DamageVsStructure","value":0.08,"fourPiece":{"arg0":"SetHeavyRound","arg1":5,"arg2":1}}</t>
+          <t>{"index":10,"id":"hammerfall","stat":"DamageVsStructure","value":0.08,"fourPiece":{"arg0":"SetHeavyRound","arg1":5.0,"arg2":1}}</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{"index":7,"id":"hivemind","stat":"SummonPower","value":0.1,"fourPiece":{"arg0":"SetSwarm","arg1":10}}</t>
+          <t>{"index":7,"id":"hivemind","stat":"SummonPower","value":0.1,"fourPiece":{"arg0":"SetSwarm","arg1":10.0}}</t>
         </is>
       </c>
     </row>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>{"index":3,"id":"vulcan","stat":"BurnDamage","value":0.15,"fourPiece":{"arg0":"SetFirestorm","arg1":0.1,"arg2":6}}</t>
+          <t>{"index":3,"id":"vulcan","stat":"BurnDamage","value":0.15,"fourPiece":{"arg0":"SetFirestorm","arg1":0.1,"arg2":6.0}}</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1;1.5;2;2.5;3</t>
+          <t>1;1.5;2.0;2.5;3.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{"id":"engineer_bay","slot":"TowerStructure","branches":"NoBranch","implicitStat":"RegenDelay","top":[1,1.5,2,2.5,3],"Main":"Regen"}</t>
+          <t>{"id":"engineer_bay","slot":"TowerStructure","branches":"NoBranch","implicitStat":"RegenDelay","top":[1,1.5,2.0,2.5,3.0],"Main":"Regen"}</t>
         </is>
       </c>
     </row>
@@ -16927,12 +16927,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"id":"TowerCounterBattery","slot":"TowerSystems","branches":"NoBranch","epic":[4],"legendary":[6]}</t>
+          <t>{"id":"TowerCounterBattery","slot":"TowerSystems","branches":"NoBranch","epic":[4.0],"legendary":[6.0]}</t>
         </is>
       </c>
     </row>
